--- a/apps/backend/issuereturn_library_migration.xlsx
+++ b/apps/backend/issuereturn_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="177">
   <si>
     <t>legacy_id</t>
   </si>
@@ -143,6 +143,405 @@
   </si>
   <si>
     <t>2026-05-14T05:24:04.769Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:22.671Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:25.131Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:26.137Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:27.171Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:28.167Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:29.032Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:36.720Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:43.053Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:44.477Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:07:50.988Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:00.606Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:09.997Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:14.953Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:22.718Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:27.058Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:30.089Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:30.797Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:36.770Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:44.634Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:08:57.647Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:03.377Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:07.479Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:11.331Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:15.512Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:16.296Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:17.064Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:17.820Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:22.891Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:32.476Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:36.853Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:41.281Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:45.247Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:49.152Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:54.329Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:09:57.652Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:01.371Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:04.887Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:08.823Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:14.691Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:23.512Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:29.069Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:30.312Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:38.201Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:43.349Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:46.909Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:10:52.967Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:11:01.396Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:11:03.050Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:11:06.221Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:11:12.979Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:11:24.880Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:11:40.445Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:11:48.351Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:12:01.350Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:12:04.839Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:12:08.518Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:12:12.194Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:12:18.813Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:12:30.702Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:12:44.241Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:12:52.101Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:12:53.533Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:13:14.159Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:13:19.216Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:13:51.098Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:13:53.123Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:13:54.710Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:14:00.439Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:14:01.658Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:14:02.831Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:14:07.284Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:14:08.471Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:14:21.617Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:14:28.561Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:15:15.980Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:15:28.039Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:15:50.799Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:15:52.329Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:16:49.457Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:16:59.378Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:17:08.444Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:17:14.862Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:17:20.529Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:17:24.918Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:17:31.210Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:17:36.714Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:17:59.501Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:03.484Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:04.346Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:12.538Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:13.621Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:23.222Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:28.518Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:34.830Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:35.794Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:48.055Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:52.188Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:55.675Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:18:59.666Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:05.027Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:18.373Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:23.664Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:24.492Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:25.727Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:30.619Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:35.760Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:36.537Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:41.327Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:48.414Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:53.717Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:19:58.436Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:09.274Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:12.188Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:19.164Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:24.060Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:27.344Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:30.710Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:35.526Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:38.788Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:42.072Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:46.178Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:50.908Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:55.173Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:20:59.166Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:21:02.542Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:21:08.127Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:21:13.188Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:21:19.030Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:21:24.002Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:21:29.033Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:21:32.833Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:21:36.836Z</t>
+  </si>
+  <si>
+    <t>2026-05-16T06:21:44.969Z</t>
   </si>
 </sst>
 </file>
@@ -523,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1044,6 +1443,1868 @@
         <v>43</v>
       </c>
     </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>36130</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>36982</v>
+      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>37243</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>38017</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>38021</v>
+      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>39441</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>39797</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>39800</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>39804</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>39998</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>40023</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>40024</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>40025</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>40055</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>40701</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>40702</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>40721</v>
+      </c>
+      <c r="B54" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>40722</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>40723</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>40753</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>40754</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>40800</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>40801</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>40802</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>40996</v>
+      </c>
+      <c r="B62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>41181</v>
+      </c>
+      <c r="B63" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>41182</v>
+      </c>
+      <c r="B64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>41301</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>41302</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>41406</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>41436</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>41445</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>41456</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>41457</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>41458</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>41459</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>41566</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>41567</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>41568</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>41639</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>41640</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>41696</v>
+      </c>
+      <c r="B79" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>41821</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>41824</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>41850</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>41851</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>41940</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>41952</v>
+      </c>
+      <c r="B85" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>41953</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>41970</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>41971</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>41972</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>41973</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>42066</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>42067</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>42068</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>42102</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>42120</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>42121</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>42258</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>42259</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>42439</v>
+      </c>
+      <c r="B99" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>42526</v>
+      </c>
+      <c r="B100" t="s">
+        <v>4</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>42527</v>
+      </c>
+      <c r="B101" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>42528</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>42669</v>
+      </c>
+      <c r="B103" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>42802</v>
+      </c>
+      <c r="B104" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" t="s">
+        <v>14</v>
+      </c>
+      <c r="D104" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>42852</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+      <c r="D105" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>42854</v>
+      </c>
+      <c r="B106" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>42855</v>
+      </c>
+      <c r="B107" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>42856</v>
+      </c>
+      <c r="B108" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>43251</v>
+      </c>
+      <c r="B109" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" t="s">
+        <v>14</v>
+      </c>
+      <c r="D109" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>43324</v>
+      </c>
+      <c r="B110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>43333</v>
+      </c>
+      <c r="B111" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>43439</v>
+      </c>
+      <c r="B112" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>43440</v>
+      </c>
+      <c r="B113" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>43441</v>
+      </c>
+      <c r="B114" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>43620</v>
+      </c>
+      <c r="B115" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>43622</v>
+      </c>
+      <c r="B116" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>43866</v>
+      </c>
+      <c r="B117" t="s">
+        <v>4</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>43867</v>
+      </c>
+      <c r="B118" t="s">
+        <v>4</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>43878</v>
+      </c>
+      <c r="B119" t="s">
+        <v>4</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>43879</v>
+      </c>
+      <c r="B120" t="s">
+        <v>4</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>43934</v>
+      </c>
+      <c r="B121" t="s">
+        <v>4</v>
+      </c>
+      <c r="C121" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>43941</v>
+      </c>
+      <c r="B122" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>44078</v>
+      </c>
+      <c r="B123" t="s">
+        <v>4</v>
+      </c>
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>44079</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4</v>
+      </c>
+      <c r="C124" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>44341</v>
+      </c>
+      <c r="B125" t="s">
+        <v>4</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>44376</v>
+      </c>
+      <c r="B126" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" t="s">
+        <v>14</v>
+      </c>
+      <c r="D126" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>44456</v>
+      </c>
+      <c r="B127" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>44632</v>
+      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" t="s">
+        <v>14</v>
+      </c>
+      <c r="D128" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>44633</v>
+      </c>
+      <c r="B129" t="s">
+        <v>4</v>
+      </c>
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>44652</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>44653</v>
+      </c>
+      <c r="B131" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>44662</v>
+      </c>
+      <c r="B132" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>44667</v>
+      </c>
+      <c r="B133" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>44668</v>
+      </c>
+      <c r="B134" t="s">
+        <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>44671</v>
+      </c>
+      <c r="B135" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>44678</v>
+      </c>
+      <c r="B136" t="s">
+        <v>4</v>
+      </c>
+      <c r="C136" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>44679</v>
+      </c>
+      <c r="B137" t="s">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>5</v>
+      </c>
+      <c r="D137" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>44680</v>
+      </c>
+      <c r="B138" t="s">
+        <v>4</v>
+      </c>
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>44699</v>
+      </c>
+      <c r="B139" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" t="s">
+        <v>5</v>
+      </c>
+      <c r="D139" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>44700</v>
+      </c>
+      <c r="B140" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" t="s">
+        <v>14</v>
+      </c>
+      <c r="D140" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>44711</v>
+      </c>
+      <c r="B141" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" t="s">
+        <v>14</v>
+      </c>
+      <c r="D141" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>44741</v>
+      </c>
+      <c r="B142" t="s">
+        <v>4</v>
+      </c>
+      <c r="C142" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>44827</v>
+      </c>
+      <c r="B143" t="s">
+        <v>4</v>
+      </c>
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>44859</v>
+      </c>
+      <c r="B144" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>44871</v>
+      </c>
+      <c r="B145" t="s">
+        <v>4</v>
+      </c>
+      <c r="C145" t="s">
+        <v>5</v>
+      </c>
+      <c r="D145" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>44918</v>
+      </c>
+      <c r="B146" t="s">
+        <v>4</v>
+      </c>
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>44919</v>
+      </c>
+      <c r="B147" t="s">
+        <v>4</v>
+      </c>
+      <c r="C147" t="s">
+        <v>5</v>
+      </c>
+      <c r="D147" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>45055</v>
+      </c>
+      <c r="B148" t="s">
+        <v>4</v>
+      </c>
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+      <c r="D148" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>45079</v>
+      </c>
+      <c r="B149" t="s">
+        <v>4</v>
+      </c>
+      <c r="C149" t="s">
+        <v>5</v>
+      </c>
+      <c r="D149" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>45080</v>
+      </c>
+      <c r="B150" t="s">
+        <v>4</v>
+      </c>
+      <c r="C150" t="s">
+        <v>5</v>
+      </c>
+      <c r="D150" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>45081</v>
+      </c>
+      <c r="B151" t="s">
+        <v>4</v>
+      </c>
+      <c r="C151" t="s">
+        <v>5</v>
+      </c>
+      <c r="D151" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>45082</v>
+      </c>
+      <c r="B152" t="s">
+        <v>4</v>
+      </c>
+      <c r="C152" t="s">
+        <v>5</v>
+      </c>
+      <c r="D152" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>45097</v>
+      </c>
+      <c r="B153" t="s">
+        <v>4</v>
+      </c>
+      <c r="C153" t="s">
+        <v>5</v>
+      </c>
+      <c r="D153" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>45242</v>
+      </c>
+      <c r="B154" t="s">
+        <v>4</v>
+      </c>
+      <c r="C154" t="s">
+        <v>5</v>
+      </c>
+      <c r="D154" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>45266</v>
+      </c>
+      <c r="B155" t="s">
+        <v>4</v>
+      </c>
+      <c r="C155" t="s">
+        <v>5</v>
+      </c>
+      <c r="D155" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>45276</v>
+      </c>
+      <c r="B156" t="s">
+        <v>4</v>
+      </c>
+      <c r="C156" t="s">
+        <v>5</v>
+      </c>
+      <c r="D156" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>45345</v>
+      </c>
+      <c r="B157" t="s">
+        <v>4</v>
+      </c>
+      <c r="C157" t="s">
+        <v>5</v>
+      </c>
+      <c r="D157" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>45395</v>
+      </c>
+      <c r="B158" t="s">
+        <v>4</v>
+      </c>
+      <c r="C158" t="s">
+        <v>5</v>
+      </c>
+      <c r="D158" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>45396</v>
+      </c>
+      <c r="B159" t="s">
+        <v>4</v>
+      </c>
+      <c r="C159" t="s">
+        <v>5</v>
+      </c>
+      <c r="D159" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>45435</v>
+      </c>
+      <c r="B160" t="s">
+        <v>4</v>
+      </c>
+      <c r="C160" t="s">
+        <v>5</v>
+      </c>
+      <c r="D160" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>45436</v>
+      </c>
+      <c r="B161" t="s">
+        <v>4</v>
+      </c>
+      <c r="C161" t="s">
+        <v>5</v>
+      </c>
+      <c r="D161" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>45444</v>
+      </c>
+      <c r="B162" t="s">
+        <v>4</v>
+      </c>
+      <c r="C162" t="s">
+        <v>5</v>
+      </c>
+      <c r="D162" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>45546</v>
+      </c>
+      <c r="B163" t="s">
+        <v>4</v>
+      </c>
+      <c r="C163" t="s">
+        <v>5</v>
+      </c>
+      <c r="D163" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>45547</v>
+      </c>
+      <c r="B164" t="s">
+        <v>4</v>
+      </c>
+      <c r="C164" t="s">
+        <v>5</v>
+      </c>
+      <c r="D164" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>45600</v>
+      </c>
+      <c r="B165" t="s">
+        <v>4</v>
+      </c>
+      <c r="C165" t="s">
+        <v>5</v>
+      </c>
+      <c r="D165" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>45611</v>
+      </c>
+      <c r="B166" t="s">
+        <v>4</v>
+      </c>
+      <c r="C166" t="s">
+        <v>5</v>
+      </c>
+      <c r="D166" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>45612</v>
+      </c>
+      <c r="B167" t="s">
+        <v>4</v>
+      </c>
+      <c r="C167" t="s">
+        <v>5</v>
+      </c>
+      <c r="D167" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>45655</v>
+      </c>
+      <c r="B168" t="s">
+        <v>4</v>
+      </c>
+      <c r="C168" t="s">
+        <v>5</v>
+      </c>
+      <c r="D168" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>45656</v>
+      </c>
+      <c r="B169" t="s">
+        <v>4</v>
+      </c>
+      <c r="C169" t="s">
+        <v>5</v>
+      </c>
+      <c r="D169" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>45680</v>
+      </c>
+      <c r="B170" t="s">
+        <v>4</v>
+      </c>
+      <c r="C170" t="s">
+        <v>5</v>
+      </c>
+      <c r="D170" t="s">
+        <v>176</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/apps/backend/issuereturn_library_migration.xlsx
+++ b/apps/backend/issuereturn_library_migration.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="630">
   <si>
     <t>legacy_id</t>
   </si>
@@ -542,6 +542,1365 @@
   </si>
   <si>
     <t>2026-05-16T06:21:44.969Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:24.276Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:25.043Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:26.130Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:27.114Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:28.188Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:29.159Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:29.810Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:30.613Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:31.435Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:32.280Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:33.191Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:33.909Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:34.715Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:35.572Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:36.541Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:37.321Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:38.182Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:39.519Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:40.396Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:41.357Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:42.276Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:43.249Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:44.124Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:48.049Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:49.636Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:50.673Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:51.887Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:52.858Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:20:53.946Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:21:10.962Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:21:20.965Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:21:31.671Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:21:42.201Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:21:42.977Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:21:47.363Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:21:53.213Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:21:58.352Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:21:59.356Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:03.378Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:09.519Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:13.116Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:18.749Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:22.598Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:26.761Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:31.366Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:37.842Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:42.548Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:52.014Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:22:59.875Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:04.539Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:10.983Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:12.806Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:17.772Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:22.455Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:23.317Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:31.646Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:37.234Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:42.838Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:48.326Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:53.964Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:23:59.450Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:06.820Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:11.087Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:18.550Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:25.116Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:31.342Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:32.447Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:33.385Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:37.697Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:38.844Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:43.713Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:24:53.482Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:00.474Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:04.679Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:09.716Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:16.703Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:18.008Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:23.432Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:29.923Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:31.123Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:38.892Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:43.785Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:51.312Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:57.597Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:25:58.957Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:04.744Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:11.005Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:14.443Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:20.628Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:25.017Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:25.712Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:31.306Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:34.744Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:40.353Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:41.002Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:45.918Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:50.998Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:53.990Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:26:57.658Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:02.715Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:05.869Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:09.711Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:15.166Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:22.171Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:28.175Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:34.960Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:42.945Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:48.424Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:27:54.310Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:00.065Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:04.352Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:09.239Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:14.022Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:24.106Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:32.508Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:40.329Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:41.395Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:46.469Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:50.327Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:28:57.091Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:00.736Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:06.408Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:07.442Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:12.566Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:17.348Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:21.819Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:22.712Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:26.416Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:32.301Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:38.372Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:39.490Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:46.747Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:29:48.760Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:02.697Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:08.056Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:13.325Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:14.161Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:17.969Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:22.813Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:26.779Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:32.202Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:32.802Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:33.420Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:34.126Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:35.531Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:36.305Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:37.097Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:42.748Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:30:52.081Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:31:02.797Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:31:08.699Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:31:12.050Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:31:17.893Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:31:21.708Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:31:35.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:31:50.833Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:31:52.775Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:31:57.571Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:32:03.494Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:32:17.186Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:32:27.155Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:32:34.122Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:32:44.679Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:32:48.409Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:32:55.642Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:33:02.260Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:33:07.335Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:33:13.737Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:33:21.860Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:33:30.080Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:33:35.851Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:33:40.725Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:33:50.378Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:33:57.734Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:04.451Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:06.484Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:13.324Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:19.795Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:22.770Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:28.842Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:35.411Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:39.387Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:43.987Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:51.291Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:34:57.106Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:08.117Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:13.875Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:20.667Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:27.398Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:28.455Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:29.564Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:30.801Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:36.438Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:38.044Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:39.095Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:48.753Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:35:59.592Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:09.136Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:19.173Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:26.910Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:32.238Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:33.638Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:34.768Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:46.185Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:47.976Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:49.113Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:50.279Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:51.290Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:36:58.795Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:05.643Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:10.677Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:11.603Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:16.405Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:20.062Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:23.624Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:28.446Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:32.170Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:37.423Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:41.416Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:45.753Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:50.829Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:55.562Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:37:57.124Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:04.767Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:09.495Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:20.957Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:24.811Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:25.716Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:29.761Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:34.264Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:38.734Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:42.619Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:43.561Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:47.948Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:53.953Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:38:58.458Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:04.262Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:10.523Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:12.993Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:14.852Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:21.883Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:27.630Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:32.443Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:33.346Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:34.584Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:39.991Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:44.675Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:49.720Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:55.257Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:39:59.533Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:40:06.033Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:40:12.013Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:40:18.542Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:40:24.669Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:40:34.491Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:40:41.203Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:40:44.603Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:40:50.143Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:40:51.489Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:00.092Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:06.975Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:12.437Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:18.705Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:20.301Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:25.375Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:31.320Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:35.168Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:39.967Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:41.248Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:47.520Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:53.080Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:53.750Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:41:58.957Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:04.517Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:05.338Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:09.433Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:10.283Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:11.200Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:15.519Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:19.688Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:24.381Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:28.239Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:31.663Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:36.445Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:41.363Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:44.446Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:48.472Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:53.358Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:42:57.990Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:43:05.659Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:43:14.821Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:43:22.795Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:43:36.056Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:43:37.551Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:43:45.663Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:43:53.726Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:44:03.916Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:44:13.709Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:44:23.190Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:44:29.090Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:44:38.779Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:44:50.307Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:01.534Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:10.046Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:17.576Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:32.179Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:33.551Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:41.505Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:47.725Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:55.153Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:57.005Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:45:58.037Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:01.132Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:04.985Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:06.524Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:08.225Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:09.316Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:10.336Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:20.971Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:31.727Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:34.583Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:37.478Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:43.917Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:49.540Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:54.847Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:46:55.774Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:47:01.541Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:47:13.062Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:47:20.618Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:47:29.676Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:47:31.273Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:47:40.024Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:47:44.931Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:47:50.444Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:47:57.842Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:02.954Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:08.198Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:13.119Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:19.277Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:23.246Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:27.739Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:33.317Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:38.605Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:45.490Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:51.879Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:52.886Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:58.080Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:48:58.920Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:00.116Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:04.584Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:08.903Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:13.851Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:18.090Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:24.981Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:29.916Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:35.640Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:40.251Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:45.353Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:50.579Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:49:55.250Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:00.534Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:07.421Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:13.341Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:17.958Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:24.068Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:28.285Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:34.329Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:35.563Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:41.570Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:46.117Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:51.042Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:50:56.232Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:00.674Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:05.752Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:12.123Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:18.616Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:25.418Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:30.913Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:32.240Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:33.262Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:41.261Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:47.435Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:52.012Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:51:57.240Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:07.144Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:16.730Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:22.957Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:28.408Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:33.840Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:34.864Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:40.039Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:41.068Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:42.023Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:48.559Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:52:56.741Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:01.515Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:06.934Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:12.224Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:18.048Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:23.419Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:29.410Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:34.637Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:38.413Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:45.494Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:50.161Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:53:54.566Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:00.795Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:07.582Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:14.957Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:20.494Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:21.587Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:28.898Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:34.295Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:40.536Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:47.190Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:52.465Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:54:57.810Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:03.722Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:08.565Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:15.213Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:22.419Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:29.579Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:30.615Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:35.181Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:42.117Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:48.181Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:55.108Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:55:59.792Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:06.122Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:13.003Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:19.863Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:26.136Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:32.298Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:37.308Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:42.879Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:48.451Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:54.409Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:56:59.136Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:57:05.252Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:57:11.306Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:57:16.333Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:57:21.202Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:57:27.360Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:57:32.915Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:57:39.811Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:57:44.167Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:57:49.905Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:58:12.403Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:58:24.321Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:58:33.648Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:58:42.390Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:58:47.128Z</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:58:53.934Z</t>
   </si>
 </sst>
 </file>
@@ -922,7 +2281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D623"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3305,6 +4664,6348 @@
         <v>176</v>
       </c>
     </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>36130</v>
+      </c>
+      <c r="B171" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171" t="s">
+        <v>14</v>
+      </c>
+      <c r="D171" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>36982</v>
+      </c>
+      <c r="B172" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>37243</v>
+      </c>
+      <c r="B173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" t="s">
+        <v>14</v>
+      </c>
+      <c r="D173" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>38017</v>
+      </c>
+      <c r="B174" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" t="s">
+        <v>14</v>
+      </c>
+      <c r="D174" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>38021</v>
+      </c>
+      <c r="B175" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" t="s">
+        <v>14</v>
+      </c>
+      <c r="D175" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>39441</v>
+      </c>
+      <c r="B176" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176" t="s">
+        <v>14</v>
+      </c>
+      <c r="D176" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>39804</v>
+      </c>
+      <c r="B177" t="s">
+        <v>13</v>
+      </c>
+      <c r="C177" t="s">
+        <v>14</v>
+      </c>
+      <c r="D177" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>40721</v>
+      </c>
+      <c r="B178" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>40723</v>
+      </c>
+      <c r="B179" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>40996</v>
+      </c>
+      <c r="B180" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>41181</v>
+      </c>
+      <c r="B181" t="s">
+        <v>13</v>
+      </c>
+      <c r="C181" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>41182</v>
+      </c>
+      <c r="B182" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>41696</v>
+      </c>
+      <c r="B183" t="s">
+        <v>13</v>
+      </c>
+      <c r="C183" t="s">
+        <v>14</v>
+      </c>
+      <c r="D183" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>41952</v>
+      </c>
+      <c r="B184" t="s">
+        <v>13</v>
+      </c>
+      <c r="C184" t="s">
+        <v>14</v>
+      </c>
+      <c r="D184" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>41953</v>
+      </c>
+      <c r="B185" t="s">
+        <v>13</v>
+      </c>
+      <c r="C185" t="s">
+        <v>14</v>
+      </c>
+      <c r="D185" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>42439</v>
+      </c>
+      <c r="B186" t="s">
+        <v>13</v>
+      </c>
+      <c r="C186" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>42669</v>
+      </c>
+      <c r="B187" t="s">
+        <v>13</v>
+      </c>
+      <c r="C187" t="s">
+        <v>14</v>
+      </c>
+      <c r="D187" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>42802</v>
+      </c>
+      <c r="B188" t="s">
+        <v>13</v>
+      </c>
+      <c r="C188" t="s">
+        <v>14</v>
+      </c>
+      <c r="D188" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>42854</v>
+      </c>
+      <c r="B189" t="s">
+        <v>13</v>
+      </c>
+      <c r="C189" t="s">
+        <v>14</v>
+      </c>
+      <c r="D189" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>42855</v>
+      </c>
+      <c r="B190" t="s">
+        <v>13</v>
+      </c>
+      <c r="C190" t="s">
+        <v>14</v>
+      </c>
+      <c r="D190" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>43251</v>
+      </c>
+      <c r="B191" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" t="s">
+        <v>14</v>
+      </c>
+      <c r="D191" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>43620</v>
+      </c>
+      <c r="B192" t="s">
+        <v>13</v>
+      </c>
+      <c r="C192" t="s">
+        <v>14</v>
+      </c>
+      <c r="D192" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>43622</v>
+      </c>
+      <c r="B193" t="s">
+        <v>13</v>
+      </c>
+      <c r="C193" t="s">
+        <v>14</v>
+      </c>
+      <c r="D193" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>44376</v>
+      </c>
+      <c r="B194" t="s">
+        <v>13</v>
+      </c>
+      <c r="C194" t="s">
+        <v>14</v>
+      </c>
+      <c r="D194" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>44632</v>
+      </c>
+      <c r="B195" t="s">
+        <v>13</v>
+      </c>
+      <c r="C195" t="s">
+        <v>14</v>
+      </c>
+      <c r="D195" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>44662</v>
+      </c>
+      <c r="B196" t="s">
+        <v>13</v>
+      </c>
+      <c r="C196" t="s">
+        <v>14</v>
+      </c>
+      <c r="D196" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>44700</v>
+      </c>
+      <c r="B197" t="s">
+        <v>13</v>
+      </c>
+      <c r="C197" t="s">
+        <v>14</v>
+      </c>
+      <c r="D197" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>44711</v>
+      </c>
+      <c r="B198" t="s">
+        <v>13</v>
+      </c>
+      <c r="C198" t="s">
+        <v>14</v>
+      </c>
+      <c r="D198" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>44859</v>
+      </c>
+      <c r="B199" t="s">
+        <v>13</v>
+      </c>
+      <c r="C199" t="s">
+        <v>14</v>
+      </c>
+      <c r="D199" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>45806</v>
+      </c>
+      <c r="B200" t="s">
+        <v>4</v>
+      </c>
+      <c r="C200" t="s">
+        <v>5</v>
+      </c>
+      <c r="D200" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>45879</v>
+      </c>
+      <c r="B201" t="s">
+        <v>4</v>
+      </c>
+      <c r="C201" t="s">
+        <v>5</v>
+      </c>
+      <c r="D201" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>45880</v>
+      </c>
+      <c r="B202" t="s">
+        <v>4</v>
+      </c>
+      <c r="C202" t="s">
+        <v>5</v>
+      </c>
+      <c r="D202" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>45881</v>
+      </c>
+      <c r="B203" t="s">
+        <v>4</v>
+      </c>
+      <c r="C203" t="s">
+        <v>5</v>
+      </c>
+      <c r="D203" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>46018</v>
+      </c>
+      <c r="B204" t="s">
+        <v>13</v>
+      </c>
+      <c r="C204" t="s">
+        <v>14</v>
+      </c>
+      <c r="D204" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>46111</v>
+      </c>
+      <c r="B205" t="s">
+        <v>4</v>
+      </c>
+      <c r="C205" t="s">
+        <v>5</v>
+      </c>
+      <c r="D205" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>46169</v>
+      </c>
+      <c r="B206" t="s">
+        <v>4</v>
+      </c>
+      <c r="C206" t="s">
+        <v>5</v>
+      </c>
+      <c r="D206" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>46212</v>
+      </c>
+      <c r="B207" t="s">
+        <v>4</v>
+      </c>
+      <c r="C207" t="s">
+        <v>5</v>
+      </c>
+      <c r="D207" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>46402</v>
+      </c>
+      <c r="B208" t="s">
+        <v>13</v>
+      </c>
+      <c r="C208" t="s">
+        <v>14</v>
+      </c>
+      <c r="D208" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>46413</v>
+      </c>
+      <c r="B209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" t="s">
+        <v>14</v>
+      </c>
+      <c r="D209" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>46559</v>
+      </c>
+      <c r="B210" t="s">
+        <v>4</v>
+      </c>
+      <c r="C210" t="s">
+        <v>5</v>
+      </c>
+      <c r="D210" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>46590</v>
+      </c>
+      <c r="B211" t="s">
+        <v>4</v>
+      </c>
+      <c r="C211" t="s">
+        <v>5</v>
+      </c>
+      <c r="D211" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>46591</v>
+      </c>
+      <c r="B212" t="s">
+        <v>4</v>
+      </c>
+      <c r="C212" t="s">
+        <v>5</v>
+      </c>
+      <c r="D212" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>46592</v>
+      </c>
+      <c r="B213" t="s">
+        <v>4</v>
+      </c>
+      <c r="C213" t="s">
+        <v>5</v>
+      </c>
+      <c r="D213" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>46593</v>
+      </c>
+      <c r="B214" t="s">
+        <v>4</v>
+      </c>
+      <c r="C214" t="s">
+        <v>5</v>
+      </c>
+      <c r="D214" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>46681</v>
+      </c>
+      <c r="B215" t="s">
+        <v>4</v>
+      </c>
+      <c r="C215" t="s">
+        <v>5</v>
+      </c>
+      <c r="D215" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>46800</v>
+      </c>
+      <c r="B216" t="s">
+        <v>4</v>
+      </c>
+      <c r="C216" t="s">
+        <v>5</v>
+      </c>
+      <c r="D216" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>46863</v>
+      </c>
+      <c r="B217" t="s">
+        <v>4</v>
+      </c>
+      <c r="C217" t="s">
+        <v>5</v>
+      </c>
+      <c r="D217" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>46869</v>
+      </c>
+      <c r="B218" t="s">
+        <v>4</v>
+      </c>
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>46870</v>
+      </c>
+      <c r="B219" t="s">
+        <v>4</v>
+      </c>
+      <c r="C219" t="s">
+        <v>5</v>
+      </c>
+      <c r="D219" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>47122</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4</v>
+      </c>
+      <c r="C220" t="s">
+        <v>5</v>
+      </c>
+      <c r="D220" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>47141</v>
+      </c>
+      <c r="B221" t="s">
+        <v>13</v>
+      </c>
+      <c r="C221" t="s">
+        <v>14</v>
+      </c>
+      <c r="D221" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>47199</v>
+      </c>
+      <c r="B222" t="s">
+        <v>13</v>
+      </c>
+      <c r="C222" t="s">
+        <v>14</v>
+      </c>
+      <c r="D222" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>47266</v>
+      </c>
+      <c r="B223" t="s">
+        <v>4</v>
+      </c>
+      <c r="C223" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>47267</v>
+      </c>
+      <c r="B224" t="s">
+        <v>4</v>
+      </c>
+      <c r="C224" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>47485</v>
+      </c>
+      <c r="B225" t="s">
+        <v>13</v>
+      </c>
+      <c r="C225" t="s">
+        <v>14</v>
+      </c>
+      <c r="D225" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>47543</v>
+      </c>
+      <c r="B226" t="s">
+        <v>4</v>
+      </c>
+      <c r="C226" t="s">
+        <v>5</v>
+      </c>
+      <c r="D226" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>47580</v>
+      </c>
+      <c r="B227" t="s">
+        <v>4</v>
+      </c>
+      <c r="C227" t="s">
+        <v>5</v>
+      </c>
+      <c r="D227" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>47711</v>
+      </c>
+      <c r="B228" t="s">
+        <v>4</v>
+      </c>
+      <c r="C228" t="s">
+        <v>5</v>
+      </c>
+      <c r="D228" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>47717</v>
+      </c>
+      <c r="B229" t="s">
+        <v>4</v>
+      </c>
+      <c r="C229" t="s">
+        <v>5</v>
+      </c>
+      <c r="D229" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>47840</v>
+      </c>
+      <c r="B230" t="s">
+        <v>4</v>
+      </c>
+      <c r="C230" t="s">
+        <v>5</v>
+      </c>
+      <c r="D230" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>47873</v>
+      </c>
+      <c r="B231" t="s">
+        <v>4</v>
+      </c>
+      <c r="C231" t="s">
+        <v>5</v>
+      </c>
+      <c r="D231" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>47874</v>
+      </c>
+      <c r="B232" t="s">
+        <v>4</v>
+      </c>
+      <c r="C232" t="s">
+        <v>5</v>
+      </c>
+      <c r="D232" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>47891</v>
+      </c>
+      <c r="B233" t="s">
+        <v>4</v>
+      </c>
+      <c r="C233" t="s">
+        <v>5</v>
+      </c>
+      <c r="D233" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>47892</v>
+      </c>
+      <c r="B234" t="s">
+        <v>4</v>
+      </c>
+      <c r="C234" t="s">
+        <v>5</v>
+      </c>
+      <c r="D234" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>47893</v>
+      </c>
+      <c r="B235" t="s">
+        <v>4</v>
+      </c>
+      <c r="C235" t="s">
+        <v>5</v>
+      </c>
+      <c r="D235" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>47953</v>
+      </c>
+      <c r="B236" t="s">
+        <v>4</v>
+      </c>
+      <c r="C236" t="s">
+        <v>5</v>
+      </c>
+      <c r="D236" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>48002</v>
+      </c>
+      <c r="B237" t="s">
+        <v>13</v>
+      </c>
+      <c r="C237" t="s">
+        <v>14</v>
+      </c>
+      <c r="D237" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>48003</v>
+      </c>
+      <c r="B238" t="s">
+        <v>13</v>
+      </c>
+      <c r="C238" t="s">
+        <v>14</v>
+      </c>
+      <c r="D238" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>48029</v>
+      </c>
+      <c r="B239" t="s">
+        <v>4</v>
+      </c>
+      <c r="C239" t="s">
+        <v>5</v>
+      </c>
+      <c r="D239" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>48079</v>
+      </c>
+      <c r="B240" t="s">
+        <v>13</v>
+      </c>
+      <c r="C240" t="s">
+        <v>14</v>
+      </c>
+      <c r="D240" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>48080</v>
+      </c>
+      <c r="B241" t="s">
+        <v>13</v>
+      </c>
+      <c r="C241" t="s">
+        <v>14</v>
+      </c>
+      <c r="D241" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>48172</v>
+      </c>
+      <c r="B242" t="s">
+        <v>4</v>
+      </c>
+      <c r="C242" t="s">
+        <v>5</v>
+      </c>
+      <c r="D242" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>48192</v>
+      </c>
+      <c r="B243" t="s">
+        <v>4</v>
+      </c>
+      <c r="C243" t="s">
+        <v>5</v>
+      </c>
+      <c r="D243" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>48193</v>
+      </c>
+      <c r="B244" t="s">
+        <v>4</v>
+      </c>
+      <c r="C244" t="s">
+        <v>5</v>
+      </c>
+      <c r="D244" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>48244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>4</v>
+      </c>
+      <c r="C245" t="s">
+        <v>5</v>
+      </c>
+      <c r="D245" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>48533</v>
+      </c>
+      <c r="B246" t="s">
+        <v>4</v>
+      </c>
+      <c r="C246" t="s">
+        <v>5</v>
+      </c>
+      <c r="D246" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>48634</v>
+      </c>
+      <c r="B247" t="s">
+        <v>13</v>
+      </c>
+      <c r="C247" t="s">
+        <v>14</v>
+      </c>
+      <c r="D247" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>48639</v>
+      </c>
+      <c r="B248" t="s">
+        <v>4</v>
+      </c>
+      <c r="C248" t="s">
+        <v>5</v>
+      </c>
+      <c r="D248" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>48724</v>
+      </c>
+      <c r="B249" t="s">
+        <v>4</v>
+      </c>
+      <c r="C249" t="s">
+        <v>5</v>
+      </c>
+      <c r="D249" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>48758</v>
+      </c>
+      <c r="B250" t="s">
+        <v>13</v>
+      </c>
+      <c r="C250" t="s">
+        <v>14</v>
+      </c>
+      <c r="D250" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>48761</v>
+      </c>
+      <c r="B251" t="s">
+        <v>4</v>
+      </c>
+      <c r="C251" t="s">
+        <v>5</v>
+      </c>
+      <c r="D251" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>48762</v>
+      </c>
+      <c r="B252" t="s">
+        <v>4</v>
+      </c>
+      <c r="C252" t="s">
+        <v>5</v>
+      </c>
+      <c r="D252" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>48833</v>
+      </c>
+      <c r="B253" t="s">
+        <v>4</v>
+      </c>
+      <c r="C253" t="s">
+        <v>5</v>
+      </c>
+      <c r="D253" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>48834</v>
+      </c>
+      <c r="B254" t="s">
+        <v>4</v>
+      </c>
+      <c r="C254" t="s">
+        <v>5</v>
+      </c>
+      <c r="D254" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>48853</v>
+      </c>
+      <c r="B255" t="s">
+        <v>13</v>
+      </c>
+      <c r="C255" t="s">
+        <v>14</v>
+      </c>
+      <c r="D255" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>49014</v>
+      </c>
+      <c r="B256" t="s">
+        <v>4</v>
+      </c>
+      <c r="C256" t="s">
+        <v>5</v>
+      </c>
+      <c r="D256" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>49233</v>
+      </c>
+      <c r="B257" t="s">
+        <v>4</v>
+      </c>
+      <c r="C257" t="s">
+        <v>5</v>
+      </c>
+      <c r="D257" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>49261</v>
+      </c>
+      <c r="B258" t="s">
+        <v>4</v>
+      </c>
+      <c r="C258" t="s">
+        <v>5</v>
+      </c>
+      <c r="D258" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>49353</v>
+      </c>
+      <c r="B259" t="s">
+        <v>4</v>
+      </c>
+      <c r="C259" t="s">
+        <v>5</v>
+      </c>
+      <c r="D259" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>49366</v>
+      </c>
+      <c r="B260" t="s">
+        <v>4</v>
+      </c>
+      <c r="C260" t="s">
+        <v>5</v>
+      </c>
+      <c r="D260" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>49407</v>
+      </c>
+      <c r="B261" t="s">
+        <v>13</v>
+      </c>
+      <c r="C261" t="s">
+        <v>14</v>
+      </c>
+      <c r="D261" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>49487</v>
+      </c>
+      <c r="B262" t="s">
+        <v>4</v>
+      </c>
+      <c r="C262" t="s">
+        <v>5</v>
+      </c>
+      <c r="D262" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>49488</v>
+      </c>
+      <c r="B263" t="s">
+        <v>4</v>
+      </c>
+      <c r="C263" t="s">
+        <v>5</v>
+      </c>
+      <c r="D263" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>49622</v>
+      </c>
+      <c r="B264" t="s">
+        <v>4</v>
+      </c>
+      <c r="C264" t="s">
+        <v>5</v>
+      </c>
+      <c r="D264" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>49634</v>
+      </c>
+      <c r="B265" t="s">
+        <v>13</v>
+      </c>
+      <c r="C265" t="s">
+        <v>14</v>
+      </c>
+      <c r="D265" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>49645</v>
+      </c>
+      <c r="B266" t="s">
+        <v>4</v>
+      </c>
+      <c r="C266" t="s">
+        <v>5</v>
+      </c>
+      <c r="D266" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>49700</v>
+      </c>
+      <c r="B267" t="s">
+        <v>4</v>
+      </c>
+      <c r="C267" t="s">
+        <v>5</v>
+      </c>
+      <c r="D267" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>49707</v>
+      </c>
+      <c r="B268" t="s">
+        <v>4</v>
+      </c>
+      <c r="C268" t="s">
+        <v>5</v>
+      </c>
+      <c r="D268" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>49817</v>
+      </c>
+      <c r="B269" t="s">
+        <v>4</v>
+      </c>
+      <c r="C269" t="s">
+        <v>5</v>
+      </c>
+      <c r="D269" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>50006</v>
+      </c>
+      <c r="B270" t="s">
+        <v>4</v>
+      </c>
+      <c r="C270" t="s">
+        <v>5</v>
+      </c>
+      <c r="D270" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>50147</v>
+      </c>
+      <c r="B271" t="s">
+        <v>4</v>
+      </c>
+      <c r="C271" t="s">
+        <v>5</v>
+      </c>
+      <c r="D271" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>50177</v>
+      </c>
+      <c r="B272" t="s">
+        <v>4</v>
+      </c>
+      <c r="C272" t="s">
+        <v>5</v>
+      </c>
+      <c r="D272" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>50189</v>
+      </c>
+      <c r="B273" t="s">
+        <v>4</v>
+      </c>
+      <c r="C273" t="s">
+        <v>5</v>
+      </c>
+      <c r="D273" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>50281</v>
+      </c>
+      <c r="B274" t="s">
+        <v>4</v>
+      </c>
+      <c r="C274" t="s">
+        <v>5</v>
+      </c>
+      <c r="D274" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>50282</v>
+      </c>
+      <c r="B275" t="s">
+        <v>4</v>
+      </c>
+      <c r="C275" t="s">
+        <v>5</v>
+      </c>
+      <c r="D275" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>50505</v>
+      </c>
+      <c r="B276" t="s">
+        <v>4</v>
+      </c>
+      <c r="C276" t="s">
+        <v>5</v>
+      </c>
+      <c r="D276" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>50637</v>
+      </c>
+      <c r="B277" t="s">
+        <v>4</v>
+      </c>
+      <c r="C277" t="s">
+        <v>5</v>
+      </c>
+      <c r="D277" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>50638</v>
+      </c>
+      <c r="B278" t="s">
+        <v>4</v>
+      </c>
+      <c r="C278" t="s">
+        <v>5</v>
+      </c>
+      <c r="D278" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>50639</v>
+      </c>
+      <c r="B279" t="s">
+        <v>4</v>
+      </c>
+      <c r="C279" t="s">
+        <v>5</v>
+      </c>
+      <c r="D279" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>50877</v>
+      </c>
+      <c r="B280" t="s">
+        <v>4</v>
+      </c>
+      <c r="C280" t="s">
+        <v>5</v>
+      </c>
+      <c r="D280" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>50879</v>
+      </c>
+      <c r="B281" t="s">
+        <v>4</v>
+      </c>
+      <c r="C281" t="s">
+        <v>5</v>
+      </c>
+      <c r="D281" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>50930</v>
+      </c>
+      <c r="B282" t="s">
+        <v>4</v>
+      </c>
+      <c r="C282" t="s">
+        <v>5</v>
+      </c>
+      <c r="D282" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>50931</v>
+      </c>
+      <c r="B283" t="s">
+        <v>4</v>
+      </c>
+      <c r="C283" t="s">
+        <v>5</v>
+      </c>
+      <c r="D283" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>50932</v>
+      </c>
+      <c r="B284" t="s">
+        <v>4</v>
+      </c>
+      <c r="C284" t="s">
+        <v>5</v>
+      </c>
+      <c r="D284" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>50957</v>
+      </c>
+      <c r="B285" t="s">
+        <v>4</v>
+      </c>
+      <c r="C285" t="s">
+        <v>5</v>
+      </c>
+      <c r="D285" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>51068</v>
+      </c>
+      <c r="B286" t="s">
+        <v>4</v>
+      </c>
+      <c r="C286" t="s">
+        <v>5</v>
+      </c>
+      <c r="D286" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>51146</v>
+      </c>
+      <c r="B287" t="s">
+        <v>13</v>
+      </c>
+      <c r="C287" t="s">
+        <v>14</v>
+      </c>
+      <c r="D287" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>51197</v>
+      </c>
+      <c r="B288" t="s">
+        <v>4</v>
+      </c>
+      <c r="C288" t="s">
+        <v>5</v>
+      </c>
+      <c r="D288" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>51393</v>
+      </c>
+      <c r="B289" t="s">
+        <v>4</v>
+      </c>
+      <c r="C289" t="s">
+        <v>5</v>
+      </c>
+      <c r="D289" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>51450</v>
+      </c>
+      <c r="B290" t="s">
+        <v>4</v>
+      </c>
+      <c r="C290" t="s">
+        <v>5</v>
+      </c>
+      <c r="D290" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>51451</v>
+      </c>
+      <c r="B291" t="s">
+        <v>4</v>
+      </c>
+      <c r="C291" t="s">
+        <v>5</v>
+      </c>
+      <c r="D291" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>51454</v>
+      </c>
+      <c r="B292" t="s">
+        <v>4</v>
+      </c>
+      <c r="C292" t="s">
+        <v>5</v>
+      </c>
+      <c r="D292" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>51558</v>
+      </c>
+      <c r="B293" t="s">
+        <v>13</v>
+      </c>
+      <c r="C293" t="s">
+        <v>14</v>
+      </c>
+      <c r="D293" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>51846</v>
+      </c>
+      <c r="B294" t="s">
+        <v>4</v>
+      </c>
+      <c r="C294" t="s">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>51847</v>
+      </c>
+      <c r="B295" t="s">
+        <v>4</v>
+      </c>
+      <c r="C295" t="s">
+        <v>5</v>
+      </c>
+      <c r="D295" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>51990</v>
+      </c>
+      <c r="B296" t="s">
+        <v>4</v>
+      </c>
+      <c r="C296" t="s">
+        <v>5</v>
+      </c>
+      <c r="D296" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>51991</v>
+      </c>
+      <c r="B297" t="s">
+        <v>13</v>
+      </c>
+      <c r="C297" t="s">
+        <v>14</v>
+      </c>
+      <c r="D297" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>52000</v>
+      </c>
+      <c r="B298" t="s">
+        <v>4</v>
+      </c>
+      <c r="C298" t="s">
+        <v>5</v>
+      </c>
+      <c r="D298" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>52001</v>
+      </c>
+      <c r="B299" t="s">
+        <v>4</v>
+      </c>
+      <c r="C299" t="s">
+        <v>5</v>
+      </c>
+      <c r="D299" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>52002</v>
+      </c>
+      <c r="B300" t="s">
+        <v>4</v>
+      </c>
+      <c r="C300" t="s">
+        <v>5</v>
+      </c>
+      <c r="D300" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>52040</v>
+      </c>
+      <c r="B301" t="s">
+        <v>13</v>
+      </c>
+      <c r="C301" t="s">
+        <v>14</v>
+      </c>
+      <c r="D301" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>52182</v>
+      </c>
+      <c r="B302" t="s">
+        <v>4</v>
+      </c>
+      <c r="C302" t="s">
+        <v>5</v>
+      </c>
+      <c r="D302" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>52187</v>
+      </c>
+      <c r="B303" t="s">
+        <v>13</v>
+      </c>
+      <c r="C303" t="s">
+        <v>14</v>
+      </c>
+      <c r="D303" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>52205</v>
+      </c>
+      <c r="B304" t="s">
+        <v>4</v>
+      </c>
+      <c r="C304" t="s">
+        <v>5</v>
+      </c>
+      <c r="D304" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>52266</v>
+      </c>
+      <c r="B305" t="s">
+        <v>4</v>
+      </c>
+      <c r="C305" t="s">
+        <v>5</v>
+      </c>
+      <c r="D305" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>52270</v>
+      </c>
+      <c r="B306" t="s">
+        <v>4</v>
+      </c>
+      <c r="C306" t="s">
+        <v>5</v>
+      </c>
+      <c r="D306" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>52317</v>
+      </c>
+      <c r="B307" t="s">
+        <v>13</v>
+      </c>
+      <c r="C307" t="s">
+        <v>14</v>
+      </c>
+      <c r="D307" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>52360</v>
+      </c>
+      <c r="B308" t="s">
+        <v>4</v>
+      </c>
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+      <c r="D308" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>52378</v>
+      </c>
+      <c r="B309" t="s">
+        <v>4</v>
+      </c>
+      <c r="C309" t="s">
+        <v>5</v>
+      </c>
+      <c r="D309" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>52434</v>
+      </c>
+      <c r="B310" t="s">
+        <v>4</v>
+      </c>
+      <c r="C310" t="s">
+        <v>5</v>
+      </c>
+      <c r="D310" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>52463</v>
+      </c>
+      <c r="B311" t="s">
+        <v>4</v>
+      </c>
+      <c r="C311" t="s">
+        <v>5</v>
+      </c>
+      <c r="D311" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>52464</v>
+      </c>
+      <c r="B312" t="s">
+        <v>13</v>
+      </c>
+      <c r="C312" t="s">
+        <v>14</v>
+      </c>
+      <c r="D312" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>52465</v>
+      </c>
+      <c r="B313" t="s">
+        <v>13</v>
+      </c>
+      <c r="C313" t="s">
+        <v>14</v>
+      </c>
+      <c r="D313" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>52466</v>
+      </c>
+      <c r="B314" t="s">
+        <v>13</v>
+      </c>
+      <c r="C314" t="s">
+        <v>14</v>
+      </c>
+      <c r="D314" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>52467</v>
+      </c>
+      <c r="B315" t="s">
+        <v>13</v>
+      </c>
+      <c r="C315" t="s">
+        <v>14</v>
+      </c>
+      <c r="D315" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>52631</v>
+      </c>
+      <c r="B316" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316" t="s">
+        <v>14</v>
+      </c>
+      <c r="D316" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>52635</v>
+      </c>
+      <c r="B317" t="s">
+        <v>13</v>
+      </c>
+      <c r="C317" t="s">
+        <v>14</v>
+      </c>
+      <c r="D317" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>52672</v>
+      </c>
+      <c r="B318" t="s">
+        <v>4</v>
+      </c>
+      <c r="C318" t="s">
+        <v>5</v>
+      </c>
+      <c r="D318" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>52673</v>
+      </c>
+      <c r="B319" t="s">
+        <v>4</v>
+      </c>
+      <c r="C319" t="s">
+        <v>5</v>
+      </c>
+      <c r="D319" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>52725</v>
+      </c>
+      <c r="B320" t="s">
+        <v>4</v>
+      </c>
+      <c r="C320" t="s">
+        <v>5</v>
+      </c>
+      <c r="D320" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>52730</v>
+      </c>
+      <c r="B321" t="s">
+        <v>4</v>
+      </c>
+      <c r="C321" t="s">
+        <v>5</v>
+      </c>
+      <c r="D321" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>52923</v>
+      </c>
+      <c r="B322" t="s">
+        <v>13</v>
+      </c>
+      <c r="C322" t="s">
+        <v>14</v>
+      </c>
+      <c r="D322" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>52947</v>
+      </c>
+      <c r="B323" t="s">
+        <v>4</v>
+      </c>
+      <c r="C323" t="s">
+        <v>5</v>
+      </c>
+      <c r="D323" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>53212</v>
+      </c>
+      <c r="B324" t="s">
+        <v>4</v>
+      </c>
+      <c r="C324" t="s">
+        <v>5</v>
+      </c>
+      <c r="D324" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>53273</v>
+      </c>
+      <c r="B325" t="s">
+        <v>4</v>
+      </c>
+      <c r="C325" t="s">
+        <v>5</v>
+      </c>
+      <c r="D325" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>53487</v>
+      </c>
+      <c r="B326" t="s">
+        <v>4</v>
+      </c>
+      <c r="C326" t="s">
+        <v>5</v>
+      </c>
+      <c r="D326" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>53488</v>
+      </c>
+      <c r="B327" t="s">
+        <v>13</v>
+      </c>
+      <c r="C327" t="s">
+        <v>14</v>
+      </c>
+      <c r="D327" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>53558</v>
+      </c>
+      <c r="B328" t="s">
+        <v>4</v>
+      </c>
+      <c r="C328" t="s">
+        <v>5</v>
+      </c>
+      <c r="D328" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>53672</v>
+      </c>
+      <c r="B329" t="s">
+        <v>4</v>
+      </c>
+      <c r="C329" t="s">
+        <v>5</v>
+      </c>
+      <c r="D329" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>53842</v>
+      </c>
+      <c r="B330" t="s">
+        <v>4</v>
+      </c>
+      <c r="C330" t="s">
+        <v>5</v>
+      </c>
+      <c r="D330" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>53850</v>
+      </c>
+      <c r="B331" t="s">
+        <v>4</v>
+      </c>
+      <c r="C331" t="s">
+        <v>5</v>
+      </c>
+      <c r="D331" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>53968</v>
+      </c>
+      <c r="B332" t="s">
+        <v>4</v>
+      </c>
+      <c r="C332" t="s">
+        <v>5</v>
+      </c>
+      <c r="D332" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>53969</v>
+      </c>
+      <c r="B333" t="s">
+        <v>4</v>
+      </c>
+      <c r="C333" t="s">
+        <v>5</v>
+      </c>
+      <c r="D333" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>54159</v>
+      </c>
+      <c r="B334" t="s">
+        <v>4</v>
+      </c>
+      <c r="C334" t="s">
+        <v>5</v>
+      </c>
+      <c r="D334" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>54160</v>
+      </c>
+      <c r="B335" t="s">
+        <v>4</v>
+      </c>
+      <c r="C335" t="s">
+        <v>5</v>
+      </c>
+      <c r="D335" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>54163</v>
+      </c>
+      <c r="B336" t="s">
+        <v>4</v>
+      </c>
+      <c r="C336" t="s">
+        <v>5</v>
+      </c>
+      <c r="D336" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>54303</v>
+      </c>
+      <c r="B337" t="s">
+        <v>4</v>
+      </c>
+      <c r="C337" t="s">
+        <v>5</v>
+      </c>
+      <c r="D337" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>54304</v>
+      </c>
+      <c r="B338" t="s">
+        <v>4</v>
+      </c>
+      <c r="C338" t="s">
+        <v>5</v>
+      </c>
+      <c r="D338" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>54454</v>
+      </c>
+      <c r="B339" t="s">
+        <v>4</v>
+      </c>
+      <c r="C339" t="s">
+        <v>5</v>
+      </c>
+      <c r="D339" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>54455</v>
+      </c>
+      <c r="B340" t="s">
+        <v>4</v>
+      </c>
+      <c r="C340" t="s">
+        <v>5</v>
+      </c>
+      <c r="D340" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>54554</v>
+      </c>
+      <c r="B341" t="s">
+        <v>4</v>
+      </c>
+      <c r="C341" t="s">
+        <v>5</v>
+      </c>
+      <c r="D341" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>54555</v>
+      </c>
+      <c r="B342" t="s">
+        <v>4</v>
+      </c>
+      <c r="C342" t="s">
+        <v>5</v>
+      </c>
+      <c r="D342" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>54556</v>
+      </c>
+      <c r="B343" t="s">
+        <v>4</v>
+      </c>
+      <c r="C343" t="s">
+        <v>5</v>
+      </c>
+      <c r="D343" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>54557</v>
+      </c>
+      <c r="B344" t="s">
+        <v>4</v>
+      </c>
+      <c r="C344" t="s">
+        <v>5</v>
+      </c>
+      <c r="D344" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>54558</v>
+      </c>
+      <c r="B345" t="s">
+        <v>4</v>
+      </c>
+      <c r="C345" t="s">
+        <v>5</v>
+      </c>
+      <c r="D345" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>54596</v>
+      </c>
+      <c r="B346" t="s">
+        <v>13</v>
+      </c>
+      <c r="C346" t="s">
+        <v>14</v>
+      </c>
+      <c r="D346" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>54845</v>
+      </c>
+      <c r="B347" t="s">
+        <v>4</v>
+      </c>
+      <c r="C347" t="s">
+        <v>5</v>
+      </c>
+      <c r="D347" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>54964</v>
+      </c>
+      <c r="B348" t="s">
+        <v>4</v>
+      </c>
+      <c r="C348" t="s">
+        <v>5</v>
+      </c>
+      <c r="D348" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>55299</v>
+      </c>
+      <c r="B349" t="s">
+        <v>13</v>
+      </c>
+      <c r="C349" t="s">
+        <v>14</v>
+      </c>
+      <c r="D349" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>55300</v>
+      </c>
+      <c r="B350" t="s">
+        <v>4</v>
+      </c>
+      <c r="C350" t="s">
+        <v>5</v>
+      </c>
+      <c r="D350" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>55391</v>
+      </c>
+      <c r="B351" t="s">
+        <v>4</v>
+      </c>
+      <c r="C351" t="s">
+        <v>5</v>
+      </c>
+      <c r="D351" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>55392</v>
+      </c>
+      <c r="B352" t="s">
+        <v>4</v>
+      </c>
+      <c r="C352" t="s">
+        <v>5</v>
+      </c>
+      <c r="D352" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>55394</v>
+      </c>
+      <c r="B353" t="s">
+        <v>4</v>
+      </c>
+      <c r="C353" t="s">
+        <v>5</v>
+      </c>
+      <c r="D353" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>55513</v>
+      </c>
+      <c r="B354" t="s">
+        <v>4</v>
+      </c>
+      <c r="C354" t="s">
+        <v>5</v>
+      </c>
+      <c r="D354" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>55889</v>
+      </c>
+      <c r="B355" t="s">
+        <v>4</v>
+      </c>
+      <c r="C355" t="s">
+        <v>5</v>
+      </c>
+      <c r="D355" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>55890</v>
+      </c>
+      <c r="B356" t="s">
+        <v>4</v>
+      </c>
+      <c r="C356" t="s">
+        <v>5</v>
+      </c>
+      <c r="D356" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>56063</v>
+      </c>
+      <c r="B357" t="s">
+        <v>4</v>
+      </c>
+      <c r="C357" t="s">
+        <v>5</v>
+      </c>
+      <c r="D357" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>56064</v>
+      </c>
+      <c r="B358" t="s">
+        <v>4</v>
+      </c>
+      <c r="C358" t="s">
+        <v>5</v>
+      </c>
+      <c r="D358" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>56065</v>
+      </c>
+      <c r="B359" t="s">
+        <v>4</v>
+      </c>
+      <c r="C359" t="s">
+        <v>5</v>
+      </c>
+      <c r="D359" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>56209</v>
+      </c>
+      <c r="B360" t="s">
+        <v>13</v>
+      </c>
+      <c r="C360" t="s">
+        <v>14</v>
+      </c>
+      <c r="D360" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>56210</v>
+      </c>
+      <c r="B361" t="s">
+        <v>13</v>
+      </c>
+      <c r="C361" t="s">
+        <v>14</v>
+      </c>
+      <c r="D361" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>56211</v>
+      </c>
+      <c r="B362" t="s">
+        <v>13</v>
+      </c>
+      <c r="C362" t="s">
+        <v>14</v>
+      </c>
+      <c r="D362" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>56216</v>
+      </c>
+      <c r="B363" t="s">
+        <v>4</v>
+      </c>
+      <c r="C363" t="s">
+        <v>5</v>
+      </c>
+      <c r="D363" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>56220</v>
+      </c>
+      <c r="B364" t="s">
+        <v>13</v>
+      </c>
+      <c r="C364" t="s">
+        <v>14</v>
+      </c>
+      <c r="D364" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>56221</v>
+      </c>
+      <c r="B365" t="s">
+        <v>13</v>
+      </c>
+      <c r="C365" t="s">
+        <v>14</v>
+      </c>
+      <c r="D365" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>56222</v>
+      </c>
+      <c r="B366" t="s">
+        <v>4</v>
+      </c>
+      <c r="C366" t="s">
+        <v>5</v>
+      </c>
+      <c r="D366" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>56356</v>
+      </c>
+      <c r="B367" t="s">
+        <v>4</v>
+      </c>
+      <c r="C367" t="s">
+        <v>5</v>
+      </c>
+      <c r="D367" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>56366</v>
+      </c>
+      <c r="B368" t="s">
+        <v>4</v>
+      </c>
+      <c r="C368" t="s">
+        <v>5</v>
+      </c>
+      <c r="D368" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>56367</v>
+      </c>
+      <c r="B369" t="s">
+        <v>4</v>
+      </c>
+      <c r="C369" t="s">
+        <v>5</v>
+      </c>
+      <c r="D369" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>56372</v>
+      </c>
+      <c r="B370" t="s">
+        <v>4</v>
+      </c>
+      <c r="C370" t="s">
+        <v>5</v>
+      </c>
+      <c r="D370" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>56447</v>
+      </c>
+      <c r="B371" t="s">
+        <v>4</v>
+      </c>
+      <c r="C371" t="s">
+        <v>5</v>
+      </c>
+      <c r="D371" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>56450</v>
+      </c>
+      <c r="B372" t="s">
+        <v>13</v>
+      </c>
+      <c r="C372" t="s">
+        <v>14</v>
+      </c>
+      <c r="D372" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>56451</v>
+      </c>
+      <c r="B373" t="s">
+        <v>13</v>
+      </c>
+      <c r="C373" t="s">
+        <v>14</v>
+      </c>
+      <c r="D373" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>56517</v>
+      </c>
+      <c r="B374" t="s">
+        <v>4</v>
+      </c>
+      <c r="C374" t="s">
+        <v>5</v>
+      </c>
+      <c r="D374" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>56551</v>
+      </c>
+      <c r="B375" t="s">
+        <v>13</v>
+      </c>
+      <c r="C375" t="s">
+        <v>14</v>
+      </c>
+      <c r="D375" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>56552</v>
+      </c>
+      <c r="B376" t="s">
+        <v>13</v>
+      </c>
+      <c r="C376" t="s">
+        <v>14</v>
+      </c>
+      <c r="D376" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>56553</v>
+      </c>
+      <c r="B377" t="s">
+        <v>13</v>
+      </c>
+      <c r="C377" t="s">
+        <v>14</v>
+      </c>
+      <c r="D377" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>56554</v>
+      </c>
+      <c r="B378" t="s">
+        <v>13</v>
+      </c>
+      <c r="C378" t="s">
+        <v>14</v>
+      </c>
+      <c r="D378" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>56555</v>
+      </c>
+      <c r="B379" t="s">
+        <v>4</v>
+      </c>
+      <c r="C379" t="s">
+        <v>5</v>
+      </c>
+      <c r="D379" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>56683</v>
+      </c>
+      <c r="B380" t="s">
+        <v>4</v>
+      </c>
+      <c r="C380" t="s">
+        <v>5</v>
+      </c>
+      <c r="D380" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>56684</v>
+      </c>
+      <c r="B381" t="s">
+        <v>4</v>
+      </c>
+      <c r="C381" t="s">
+        <v>5</v>
+      </c>
+      <c r="D381" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>56705</v>
+      </c>
+      <c r="B382" t="s">
+        <v>13</v>
+      </c>
+      <c r="C382" t="s">
+        <v>14</v>
+      </c>
+      <c r="D382" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>56714</v>
+      </c>
+      <c r="B383" t="s">
+        <v>4</v>
+      </c>
+      <c r="C383" t="s">
+        <v>5</v>
+      </c>
+      <c r="D383" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>56715</v>
+      </c>
+      <c r="B384" t="s">
+        <v>4</v>
+      </c>
+      <c r="C384" t="s">
+        <v>5</v>
+      </c>
+      <c r="D384" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>56722</v>
+      </c>
+      <c r="B385" t="s">
+        <v>4</v>
+      </c>
+      <c r="C385" t="s">
+        <v>5</v>
+      </c>
+      <c r="D385" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>56723</v>
+      </c>
+      <c r="B386" t="s">
+        <v>4</v>
+      </c>
+      <c r="C386" t="s">
+        <v>5</v>
+      </c>
+      <c r="D386" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>56739</v>
+      </c>
+      <c r="B387" t="s">
+        <v>4</v>
+      </c>
+      <c r="C387" t="s">
+        <v>5</v>
+      </c>
+      <c r="D387" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>56740</v>
+      </c>
+      <c r="B388" t="s">
+        <v>4</v>
+      </c>
+      <c r="C388" t="s">
+        <v>5</v>
+      </c>
+      <c r="D388" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>56765</v>
+      </c>
+      <c r="B389" t="s">
+        <v>4</v>
+      </c>
+      <c r="C389" t="s">
+        <v>5</v>
+      </c>
+      <c r="D389" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>56842</v>
+      </c>
+      <c r="B390" t="s">
+        <v>4</v>
+      </c>
+      <c r="C390" t="s">
+        <v>5</v>
+      </c>
+      <c r="D390" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>56855</v>
+      </c>
+      <c r="B391" t="s">
+        <v>4</v>
+      </c>
+      <c r="C391" t="s">
+        <v>5</v>
+      </c>
+      <c r="D391" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>56856</v>
+      </c>
+      <c r="B392" t="s">
+        <v>4</v>
+      </c>
+      <c r="C392" t="s">
+        <v>5</v>
+      </c>
+      <c r="D392" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>57031</v>
+      </c>
+      <c r="B393" t="s">
+        <v>13</v>
+      </c>
+      <c r="C393" t="s">
+        <v>14</v>
+      </c>
+      <c r="D393" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>57042</v>
+      </c>
+      <c r="B394" t="s">
+        <v>4</v>
+      </c>
+      <c r="C394" t="s">
+        <v>5</v>
+      </c>
+      <c r="D394" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>57069</v>
+      </c>
+      <c r="B395" t="s">
+        <v>4</v>
+      </c>
+      <c r="C395" t="s">
+        <v>5</v>
+      </c>
+      <c r="D395" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>57370</v>
+      </c>
+      <c r="B396" t="s">
+        <v>4</v>
+      </c>
+      <c r="C396" t="s">
+        <v>5</v>
+      </c>
+      <c r="D396" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>57383</v>
+      </c>
+      <c r="B397" t="s">
+        <v>4</v>
+      </c>
+      <c r="C397" t="s">
+        <v>5</v>
+      </c>
+      <c r="D397" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>57471</v>
+      </c>
+      <c r="B398" t="s">
+        <v>13</v>
+      </c>
+      <c r="C398" t="s">
+        <v>14</v>
+      </c>
+      <c r="D398" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>57622</v>
+      </c>
+      <c r="B399" t="s">
+        <v>4</v>
+      </c>
+      <c r="C399" t="s">
+        <v>5</v>
+      </c>
+      <c r="D399" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>57642</v>
+      </c>
+      <c r="B400" t="s">
+        <v>4</v>
+      </c>
+      <c r="C400" t="s">
+        <v>5</v>
+      </c>
+      <c r="D400" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>57643</v>
+      </c>
+      <c r="B401" t="s">
+        <v>4</v>
+      </c>
+      <c r="C401" t="s">
+        <v>5</v>
+      </c>
+      <c r="D401" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>57644</v>
+      </c>
+      <c r="B402" t="s">
+        <v>4</v>
+      </c>
+      <c r="C402" t="s">
+        <v>5</v>
+      </c>
+      <c r="D402" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>57656</v>
+      </c>
+      <c r="B403" t="s">
+        <v>13</v>
+      </c>
+      <c r="C403" t="s">
+        <v>14</v>
+      </c>
+      <c r="D403" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>57775</v>
+      </c>
+      <c r="B404" t="s">
+        <v>4</v>
+      </c>
+      <c r="C404" t="s">
+        <v>5</v>
+      </c>
+      <c r="D404" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>57778</v>
+      </c>
+      <c r="B405" t="s">
+        <v>4</v>
+      </c>
+      <c r="C405" t="s">
+        <v>5</v>
+      </c>
+      <c r="D405" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>57784</v>
+      </c>
+      <c r="B406" t="s">
+        <v>4</v>
+      </c>
+      <c r="C406" t="s">
+        <v>5</v>
+      </c>
+      <c r="D406" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>57785</v>
+      </c>
+      <c r="B407" t="s">
+        <v>4</v>
+      </c>
+      <c r="C407" t="s">
+        <v>5</v>
+      </c>
+      <c r="D407" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>57788</v>
+      </c>
+      <c r="B408" t="s">
+        <v>4</v>
+      </c>
+      <c r="C408" t="s">
+        <v>5</v>
+      </c>
+      <c r="D408" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>57859</v>
+      </c>
+      <c r="B409" t="s">
+        <v>13</v>
+      </c>
+      <c r="C409" t="s">
+        <v>14</v>
+      </c>
+      <c r="D409" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>57860</v>
+      </c>
+      <c r="B410" t="s">
+        <v>13</v>
+      </c>
+      <c r="C410" t="s">
+        <v>14</v>
+      </c>
+      <c r="D410" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>58054</v>
+      </c>
+      <c r="B411" t="s">
+        <v>4</v>
+      </c>
+      <c r="C411" t="s">
+        <v>5</v>
+      </c>
+      <c r="D411" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>58232</v>
+      </c>
+      <c r="B412" t="s">
+        <v>4</v>
+      </c>
+      <c r="C412" t="s">
+        <v>5</v>
+      </c>
+      <c r="D412" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>58234</v>
+      </c>
+      <c r="B413" t="s">
+        <v>4</v>
+      </c>
+      <c r="C413" t="s">
+        <v>5</v>
+      </c>
+      <c r="D413" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>58262</v>
+      </c>
+      <c r="B414" t="s">
+        <v>13</v>
+      </c>
+      <c r="C414" t="s">
+        <v>14</v>
+      </c>
+      <c r="D414" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>58263</v>
+      </c>
+      <c r="B415" t="s">
+        <v>13</v>
+      </c>
+      <c r="C415" t="s">
+        <v>14</v>
+      </c>
+      <c r="D415" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A416">
+        <v>58316</v>
+      </c>
+      <c r="B416" t="s">
+        <v>4</v>
+      </c>
+      <c r="C416" t="s">
+        <v>5</v>
+      </c>
+      <c r="D416" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>58317</v>
+      </c>
+      <c r="B417" t="s">
+        <v>4</v>
+      </c>
+      <c r="C417" t="s">
+        <v>5</v>
+      </c>
+      <c r="D417" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>58318</v>
+      </c>
+      <c r="B418" t="s">
+        <v>4</v>
+      </c>
+      <c r="C418" t="s">
+        <v>5</v>
+      </c>
+      <c r="D418" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>58384</v>
+      </c>
+      <c r="B419" t="s">
+        <v>4</v>
+      </c>
+      <c r="C419" t="s">
+        <v>5</v>
+      </c>
+      <c r="D419" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>58385</v>
+      </c>
+      <c r="B420" t="s">
+        <v>4</v>
+      </c>
+      <c r="C420" t="s">
+        <v>5</v>
+      </c>
+      <c r="D420" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>58424</v>
+      </c>
+      <c r="B421" t="s">
+        <v>4</v>
+      </c>
+      <c r="C421" t="s">
+        <v>5</v>
+      </c>
+      <c r="D421" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>58601</v>
+      </c>
+      <c r="B422" t="s">
+        <v>4</v>
+      </c>
+      <c r="C422" t="s">
+        <v>5</v>
+      </c>
+      <c r="D422" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>58602</v>
+      </c>
+      <c r="B423" t="s">
+        <v>4</v>
+      </c>
+      <c r="C423" t="s">
+        <v>5</v>
+      </c>
+      <c r="D423" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>58603</v>
+      </c>
+      <c r="B424" t="s">
+        <v>4</v>
+      </c>
+      <c r="C424" t="s">
+        <v>5</v>
+      </c>
+      <c r="D424" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>58604</v>
+      </c>
+      <c r="B425" t="s">
+        <v>4</v>
+      </c>
+      <c r="C425" t="s">
+        <v>5</v>
+      </c>
+      <c r="D425" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>58605</v>
+      </c>
+      <c r="B426" t="s">
+        <v>4</v>
+      </c>
+      <c r="C426" t="s">
+        <v>5</v>
+      </c>
+      <c r="D426" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>58606</v>
+      </c>
+      <c r="B427" t="s">
+        <v>4</v>
+      </c>
+      <c r="C427" t="s">
+        <v>5</v>
+      </c>
+      <c r="D427" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>58607</v>
+      </c>
+      <c r="B428" t="s">
+        <v>4</v>
+      </c>
+      <c r="C428" t="s">
+        <v>5</v>
+      </c>
+      <c r="D428" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>58608</v>
+      </c>
+      <c r="B429" t="s">
+        <v>13</v>
+      </c>
+      <c r="C429" t="s">
+        <v>14</v>
+      </c>
+      <c r="D429" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>58610</v>
+      </c>
+      <c r="B430" t="s">
+        <v>4</v>
+      </c>
+      <c r="C430" t="s">
+        <v>5</v>
+      </c>
+      <c r="D430" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>58611</v>
+      </c>
+      <c r="B431" t="s">
+        <v>4</v>
+      </c>
+      <c r="C431" t="s">
+        <v>5</v>
+      </c>
+      <c r="D431" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>58612</v>
+      </c>
+      <c r="B432" t="s">
+        <v>4</v>
+      </c>
+      <c r="C432" t="s">
+        <v>5</v>
+      </c>
+      <c r="D432" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>58613</v>
+      </c>
+      <c r="B433" t="s">
+        <v>4</v>
+      </c>
+      <c r="C433" t="s">
+        <v>5</v>
+      </c>
+      <c r="D433" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>58614</v>
+      </c>
+      <c r="B434" t="s">
+        <v>13</v>
+      </c>
+      <c r="C434" t="s">
+        <v>14</v>
+      </c>
+      <c r="D434" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>58615</v>
+      </c>
+      <c r="B435" t="s">
+        <v>4</v>
+      </c>
+      <c r="C435" t="s">
+        <v>5</v>
+      </c>
+      <c r="D435" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>58617</v>
+      </c>
+      <c r="B436" t="s">
+        <v>4</v>
+      </c>
+      <c r="C436" t="s">
+        <v>5</v>
+      </c>
+      <c r="D436" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>58618</v>
+      </c>
+      <c r="B437" t="s">
+        <v>4</v>
+      </c>
+      <c r="C437" t="s">
+        <v>5</v>
+      </c>
+      <c r="D437" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>58619</v>
+      </c>
+      <c r="B438" t="s">
+        <v>4</v>
+      </c>
+      <c r="C438" t="s">
+        <v>5</v>
+      </c>
+      <c r="D438" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>58626</v>
+      </c>
+      <c r="B439" t="s">
+        <v>13</v>
+      </c>
+      <c r="C439" t="s">
+        <v>14</v>
+      </c>
+      <c r="D439" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>58778</v>
+      </c>
+      <c r="B440" t="s">
+        <v>4</v>
+      </c>
+      <c r="C440" t="s">
+        <v>5</v>
+      </c>
+      <c r="D440" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>58779</v>
+      </c>
+      <c r="B441" t="s">
+        <v>4</v>
+      </c>
+      <c r="C441" t="s">
+        <v>5</v>
+      </c>
+      <c r="D441" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>58902</v>
+      </c>
+      <c r="B442" t="s">
+        <v>13</v>
+      </c>
+      <c r="C442" t="s">
+        <v>14</v>
+      </c>
+      <c r="D442" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>59141</v>
+      </c>
+      <c r="B443" t="s">
+        <v>4</v>
+      </c>
+      <c r="C443" t="s">
+        <v>5</v>
+      </c>
+      <c r="D443" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>59206</v>
+      </c>
+      <c r="B444" t="s">
+        <v>4</v>
+      </c>
+      <c r="C444" t="s">
+        <v>5</v>
+      </c>
+      <c r="D444" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>59371</v>
+      </c>
+      <c r="B445" t="s">
+        <v>13</v>
+      </c>
+      <c r="C445" t="s">
+        <v>14</v>
+      </c>
+      <c r="D445" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>59372</v>
+      </c>
+      <c r="B446" t="s">
+        <v>13</v>
+      </c>
+      <c r="C446" t="s">
+        <v>14</v>
+      </c>
+      <c r="D446" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>59551</v>
+      </c>
+      <c r="B447" t="s">
+        <v>13</v>
+      </c>
+      <c r="C447" t="s">
+        <v>14</v>
+      </c>
+      <c r="D447" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>59552</v>
+      </c>
+      <c r="B448" t="s">
+        <v>13</v>
+      </c>
+      <c r="C448" t="s">
+        <v>14</v>
+      </c>
+      <c r="D448" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>60131</v>
+      </c>
+      <c r="B449" t="s">
+        <v>4</v>
+      </c>
+      <c r="C449" t="s">
+        <v>5</v>
+      </c>
+      <c r="D449" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>60132</v>
+      </c>
+      <c r="B450" t="s">
+        <v>4</v>
+      </c>
+      <c r="C450" t="s">
+        <v>5</v>
+      </c>
+      <c r="D450" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>60133</v>
+      </c>
+      <c r="B451" t="s">
+        <v>4</v>
+      </c>
+      <c r="C451" t="s">
+        <v>5</v>
+      </c>
+      <c r="D451" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>60185</v>
+      </c>
+      <c r="B452" t="s">
+        <v>4</v>
+      </c>
+      <c r="C452" t="s">
+        <v>5</v>
+      </c>
+      <c r="D452" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>60246</v>
+      </c>
+      <c r="B453" t="s">
+        <v>4</v>
+      </c>
+      <c r="C453" t="s">
+        <v>5</v>
+      </c>
+      <c r="D453" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>60247</v>
+      </c>
+      <c r="B454" t="s">
+        <v>4</v>
+      </c>
+      <c r="C454" t="s">
+        <v>5</v>
+      </c>
+      <c r="D454" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>60294</v>
+      </c>
+      <c r="B455" t="s">
+        <v>4</v>
+      </c>
+      <c r="C455" t="s">
+        <v>5</v>
+      </c>
+      <c r="D455" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>60327</v>
+      </c>
+      <c r="B456" t="s">
+        <v>4</v>
+      </c>
+      <c r="C456" t="s">
+        <v>5</v>
+      </c>
+      <c r="D456" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>60330</v>
+      </c>
+      <c r="B457" t="s">
+        <v>4</v>
+      </c>
+      <c r="C457" t="s">
+        <v>5</v>
+      </c>
+      <c r="D457" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>60345</v>
+      </c>
+      <c r="B458" t="s">
+        <v>4</v>
+      </c>
+      <c r="C458" t="s">
+        <v>5</v>
+      </c>
+      <c r="D458" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>60374</v>
+      </c>
+      <c r="B459" t="s">
+        <v>4</v>
+      </c>
+      <c r="C459" t="s">
+        <v>5</v>
+      </c>
+      <c r="D459" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>60515</v>
+      </c>
+      <c r="B460" t="s">
+        <v>4</v>
+      </c>
+      <c r="C460" t="s">
+        <v>5</v>
+      </c>
+      <c r="D460" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>60648</v>
+      </c>
+      <c r="B461" t="s">
+        <v>4</v>
+      </c>
+      <c r="C461" t="s">
+        <v>5</v>
+      </c>
+      <c r="D461" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>60649</v>
+      </c>
+      <c r="B462" t="s">
+        <v>4</v>
+      </c>
+      <c r="C462" t="s">
+        <v>5</v>
+      </c>
+      <c r="D462" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>60665</v>
+      </c>
+      <c r="B463" t="s">
+        <v>4</v>
+      </c>
+      <c r="C463" t="s">
+        <v>5</v>
+      </c>
+      <c r="D463" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A464">
+        <v>60703</v>
+      </c>
+      <c r="B464" t="s">
+        <v>13</v>
+      </c>
+      <c r="C464" t="s">
+        <v>14</v>
+      </c>
+      <c r="D464" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <v>60705</v>
+      </c>
+      <c r="B465" t="s">
+        <v>4</v>
+      </c>
+      <c r="C465" t="s">
+        <v>5</v>
+      </c>
+      <c r="D465" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>60759</v>
+      </c>
+      <c r="B466" t="s">
+        <v>4</v>
+      </c>
+      <c r="C466" t="s">
+        <v>5</v>
+      </c>
+      <c r="D466" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <v>60760</v>
+      </c>
+      <c r="B467" t="s">
+        <v>4</v>
+      </c>
+      <c r="C467" t="s">
+        <v>5</v>
+      </c>
+      <c r="D467" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>60809</v>
+      </c>
+      <c r="B468" t="s">
+        <v>4</v>
+      </c>
+      <c r="C468" t="s">
+        <v>5</v>
+      </c>
+      <c r="D468" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <v>60810</v>
+      </c>
+      <c r="B469" t="s">
+        <v>4</v>
+      </c>
+      <c r="C469" t="s">
+        <v>5</v>
+      </c>
+      <c r="D469" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A470">
+        <v>60851</v>
+      </c>
+      <c r="B470" t="s">
+        <v>4</v>
+      </c>
+      <c r="C470" t="s">
+        <v>5</v>
+      </c>
+      <c r="D470" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A471">
+        <v>60852</v>
+      </c>
+      <c r="B471" t="s">
+        <v>4</v>
+      </c>
+      <c r="C471" t="s">
+        <v>5</v>
+      </c>
+      <c r="D471" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>61000</v>
+      </c>
+      <c r="B472" t="s">
+        <v>4</v>
+      </c>
+      <c r="C472" t="s">
+        <v>5</v>
+      </c>
+      <c r="D472" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A473">
+        <v>61124</v>
+      </c>
+      <c r="B473" t="s">
+        <v>4</v>
+      </c>
+      <c r="C473" t="s">
+        <v>5</v>
+      </c>
+      <c r="D473" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A474">
+        <v>61215</v>
+      </c>
+      <c r="B474" t="s">
+        <v>4</v>
+      </c>
+      <c r="C474" t="s">
+        <v>5</v>
+      </c>
+      <c r="D474" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>61216</v>
+      </c>
+      <c r="B475" t="s">
+        <v>4</v>
+      </c>
+      <c r="C475" t="s">
+        <v>5</v>
+      </c>
+      <c r="D475" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>61217</v>
+      </c>
+      <c r="B476" t="s">
+        <v>4</v>
+      </c>
+      <c r="C476" t="s">
+        <v>5</v>
+      </c>
+      <c r="D476" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A477">
+        <v>61231</v>
+      </c>
+      <c r="B477" t="s">
+        <v>13</v>
+      </c>
+      <c r="C477" t="s">
+        <v>14</v>
+      </c>
+      <c r="D477" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A478">
+        <v>61253</v>
+      </c>
+      <c r="B478" t="s">
+        <v>4</v>
+      </c>
+      <c r="C478" t="s">
+        <v>5</v>
+      </c>
+      <c r="D478" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A479">
+        <v>61261</v>
+      </c>
+      <c r="B479" t="s">
+        <v>4</v>
+      </c>
+      <c r="C479" t="s">
+        <v>5</v>
+      </c>
+      <c r="D479" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>61383</v>
+      </c>
+      <c r="B480" t="s">
+        <v>4</v>
+      </c>
+      <c r="C480" t="s">
+        <v>5</v>
+      </c>
+      <c r="D480" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A481">
+        <v>61387</v>
+      </c>
+      <c r="B481" t="s">
+        <v>13</v>
+      </c>
+      <c r="C481" t="s">
+        <v>14</v>
+      </c>
+      <c r="D481" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>61470</v>
+      </c>
+      <c r="B482" t="s">
+        <v>13</v>
+      </c>
+      <c r="C482" t="s">
+        <v>14</v>
+      </c>
+      <c r="D482" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A483">
+        <v>61471</v>
+      </c>
+      <c r="B483" t="s">
+        <v>13</v>
+      </c>
+      <c r="C483" t="s">
+        <v>14</v>
+      </c>
+      <c r="D483" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>61472</v>
+      </c>
+      <c r="B484" t="s">
+        <v>13</v>
+      </c>
+      <c r="C484" t="s">
+        <v>14</v>
+      </c>
+      <c r="D484" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A485">
+        <v>61473</v>
+      </c>
+      <c r="B485" t="s">
+        <v>13</v>
+      </c>
+      <c r="C485" t="s">
+        <v>14</v>
+      </c>
+      <c r="D485" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A486">
+        <v>61474</v>
+      </c>
+      <c r="B486" t="s">
+        <v>13</v>
+      </c>
+      <c r="C486" t="s">
+        <v>14</v>
+      </c>
+      <c r="D486" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A487">
+        <v>61503</v>
+      </c>
+      <c r="B487" t="s">
+        <v>13</v>
+      </c>
+      <c r="C487" t="s">
+        <v>14</v>
+      </c>
+      <c r="D487" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A488">
+        <v>61504</v>
+      </c>
+      <c r="B488" t="s">
+        <v>13</v>
+      </c>
+      <c r="C488" t="s">
+        <v>14</v>
+      </c>
+      <c r="D488" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A489">
+        <v>61547</v>
+      </c>
+      <c r="B489" t="s">
+        <v>4</v>
+      </c>
+      <c r="C489" t="s">
+        <v>5</v>
+      </c>
+      <c r="D489" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A490">
+        <v>61621</v>
+      </c>
+      <c r="B490" t="s">
+        <v>4</v>
+      </c>
+      <c r="C490" t="s">
+        <v>5</v>
+      </c>
+      <c r="D490" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A491">
+        <v>61680</v>
+      </c>
+      <c r="B491" t="s">
+        <v>13</v>
+      </c>
+      <c r="C491" t="s">
+        <v>14</v>
+      </c>
+      <c r="D491" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A492">
+        <v>61691</v>
+      </c>
+      <c r="B492" t="s">
+        <v>13</v>
+      </c>
+      <c r="C492" t="s">
+        <v>14</v>
+      </c>
+      <c r="D492" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A493">
+        <v>61735</v>
+      </c>
+      <c r="B493" t="s">
+        <v>4</v>
+      </c>
+      <c r="C493" t="s">
+        <v>5</v>
+      </c>
+      <c r="D493" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A494">
+        <v>61845</v>
+      </c>
+      <c r="B494" t="s">
+        <v>4</v>
+      </c>
+      <c r="C494" t="s">
+        <v>5</v>
+      </c>
+      <c r="D494" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A495">
+        <v>61970</v>
+      </c>
+      <c r="B495" t="s">
+        <v>4</v>
+      </c>
+      <c r="C495" t="s">
+        <v>5</v>
+      </c>
+      <c r="D495" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A496">
+        <v>62378</v>
+      </c>
+      <c r="B496" t="s">
+        <v>13</v>
+      </c>
+      <c r="C496" t="s">
+        <v>14</v>
+      </c>
+      <c r="D496" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A497">
+        <v>62409</v>
+      </c>
+      <c r="B497" t="s">
+        <v>4</v>
+      </c>
+      <c r="C497" t="s">
+        <v>5</v>
+      </c>
+      <c r="D497" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A498">
+        <v>62412</v>
+      </c>
+      <c r="B498" t="s">
+        <v>4</v>
+      </c>
+      <c r="C498" t="s">
+        <v>5</v>
+      </c>
+      <c r="D498" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A499">
+        <v>62538</v>
+      </c>
+      <c r="B499" t="s">
+        <v>4</v>
+      </c>
+      <c r="C499" t="s">
+        <v>5</v>
+      </c>
+      <c r="D499" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500">
+        <v>62549</v>
+      </c>
+      <c r="B500" t="s">
+        <v>13</v>
+      </c>
+      <c r="C500" t="s">
+        <v>14</v>
+      </c>
+      <c r="D500" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501">
+        <v>62562</v>
+      </c>
+      <c r="B501" t="s">
+        <v>13</v>
+      </c>
+      <c r="C501" t="s">
+        <v>14</v>
+      </c>
+      <c r="D501" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502">
+        <v>62780</v>
+      </c>
+      <c r="B502" t="s">
+        <v>4</v>
+      </c>
+      <c r="C502" t="s">
+        <v>5</v>
+      </c>
+      <c r="D502" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503">
+        <v>62781</v>
+      </c>
+      <c r="B503" t="s">
+        <v>4</v>
+      </c>
+      <c r="C503" t="s">
+        <v>5</v>
+      </c>
+      <c r="D503" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504">
+        <v>62782</v>
+      </c>
+      <c r="B504" t="s">
+        <v>4</v>
+      </c>
+      <c r="C504" t="s">
+        <v>5</v>
+      </c>
+      <c r="D504" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505">
+        <v>62783</v>
+      </c>
+      <c r="B505" t="s">
+        <v>4</v>
+      </c>
+      <c r="C505" t="s">
+        <v>5</v>
+      </c>
+      <c r="D505" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506">
+        <v>62816</v>
+      </c>
+      <c r="B506" t="s">
+        <v>4</v>
+      </c>
+      <c r="C506" t="s">
+        <v>5</v>
+      </c>
+      <c r="D506" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A507">
+        <v>62923</v>
+      </c>
+      <c r="B507" t="s">
+        <v>4</v>
+      </c>
+      <c r="C507" t="s">
+        <v>5</v>
+      </c>
+      <c r="D507" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A508">
+        <v>62924</v>
+      </c>
+      <c r="B508" t="s">
+        <v>4</v>
+      </c>
+      <c r="C508" t="s">
+        <v>5</v>
+      </c>
+      <c r="D508" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A509">
+        <v>62940</v>
+      </c>
+      <c r="B509" t="s">
+        <v>4</v>
+      </c>
+      <c r="C509" t="s">
+        <v>5</v>
+      </c>
+      <c r="D509" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A510">
+        <v>63130</v>
+      </c>
+      <c r="B510" t="s">
+        <v>4</v>
+      </c>
+      <c r="C510" t="s">
+        <v>5</v>
+      </c>
+      <c r="D510" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A511">
+        <v>63213</v>
+      </c>
+      <c r="B511" t="s">
+        <v>4</v>
+      </c>
+      <c r="C511" t="s">
+        <v>5</v>
+      </c>
+      <c r="D511" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A512">
+        <v>63214</v>
+      </c>
+      <c r="B512" t="s">
+        <v>4</v>
+      </c>
+      <c r="C512" t="s">
+        <v>5</v>
+      </c>
+      <c r="D512" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A513">
+        <v>63327</v>
+      </c>
+      <c r="B513" t="s">
+        <v>4</v>
+      </c>
+      <c r="C513" t="s">
+        <v>5</v>
+      </c>
+      <c r="D513" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A514">
+        <v>63470</v>
+      </c>
+      <c r="B514" t="s">
+        <v>4</v>
+      </c>
+      <c r="C514" t="s">
+        <v>5</v>
+      </c>
+      <c r="D514" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A515">
+        <v>63471</v>
+      </c>
+      <c r="B515" t="s">
+        <v>4</v>
+      </c>
+      <c r="C515" t="s">
+        <v>5</v>
+      </c>
+      <c r="D515" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A516">
+        <v>63488</v>
+      </c>
+      <c r="B516" t="s">
+        <v>13</v>
+      </c>
+      <c r="C516" t="s">
+        <v>14</v>
+      </c>
+      <c r="D516" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A517">
+        <v>63588</v>
+      </c>
+      <c r="B517" t="s">
+        <v>4</v>
+      </c>
+      <c r="C517" t="s">
+        <v>5</v>
+      </c>
+      <c r="D517" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A518">
+        <v>63604</v>
+      </c>
+      <c r="B518" t="s">
+        <v>13</v>
+      </c>
+      <c r="C518" t="s">
+        <v>14</v>
+      </c>
+      <c r="D518" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A519">
+        <v>63605</v>
+      </c>
+      <c r="B519" t="s">
+        <v>13</v>
+      </c>
+      <c r="C519" t="s">
+        <v>14</v>
+      </c>
+      <c r="D519" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A520">
+        <v>63606</v>
+      </c>
+      <c r="B520" t="s">
+        <v>4</v>
+      </c>
+      <c r="C520" t="s">
+        <v>5</v>
+      </c>
+      <c r="D520" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A521">
+        <v>63608</v>
+      </c>
+      <c r="B521" t="s">
+        <v>4</v>
+      </c>
+      <c r="C521" t="s">
+        <v>5</v>
+      </c>
+      <c r="D521" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A522">
+        <v>63609</v>
+      </c>
+      <c r="B522" t="s">
+        <v>4</v>
+      </c>
+      <c r="C522" t="s">
+        <v>5</v>
+      </c>
+      <c r="D522" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A523">
+        <v>63610</v>
+      </c>
+      <c r="B523" t="s">
+        <v>4</v>
+      </c>
+      <c r="C523" t="s">
+        <v>5</v>
+      </c>
+      <c r="D523" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A524">
+        <v>63771</v>
+      </c>
+      <c r="B524" t="s">
+        <v>4</v>
+      </c>
+      <c r="C524" t="s">
+        <v>5</v>
+      </c>
+      <c r="D524" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A525">
+        <v>64022</v>
+      </c>
+      <c r="B525" t="s">
+        <v>4</v>
+      </c>
+      <c r="C525" t="s">
+        <v>5</v>
+      </c>
+      <c r="D525" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A526">
+        <v>64023</v>
+      </c>
+      <c r="B526" t="s">
+        <v>4</v>
+      </c>
+      <c r="C526" t="s">
+        <v>5</v>
+      </c>
+      <c r="D526" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A527">
+        <v>64079</v>
+      </c>
+      <c r="B527" t="s">
+        <v>4</v>
+      </c>
+      <c r="C527" t="s">
+        <v>5</v>
+      </c>
+      <c r="D527" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A528">
+        <v>64130</v>
+      </c>
+      <c r="B528" t="s">
+        <v>4</v>
+      </c>
+      <c r="C528" t="s">
+        <v>5</v>
+      </c>
+      <c r="D528" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A529">
+        <v>64528</v>
+      </c>
+      <c r="B529" t="s">
+        <v>4</v>
+      </c>
+      <c r="C529" t="s">
+        <v>5</v>
+      </c>
+      <c r="D529" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A530">
+        <v>64529</v>
+      </c>
+      <c r="B530" t="s">
+        <v>4</v>
+      </c>
+      <c r="C530" t="s">
+        <v>5</v>
+      </c>
+      <c r="D530" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A531">
+        <v>64530</v>
+      </c>
+      <c r="B531" t="s">
+        <v>4</v>
+      </c>
+      <c r="C531" t="s">
+        <v>5</v>
+      </c>
+      <c r="D531" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A532">
+        <v>64589</v>
+      </c>
+      <c r="B532" t="s">
+        <v>4</v>
+      </c>
+      <c r="C532" t="s">
+        <v>5</v>
+      </c>
+      <c r="D532" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A533">
+        <v>64590</v>
+      </c>
+      <c r="B533" t="s">
+        <v>4</v>
+      </c>
+      <c r="C533" t="s">
+        <v>5</v>
+      </c>
+      <c r="D533" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A534">
+        <v>64591</v>
+      </c>
+      <c r="B534" t="s">
+        <v>4</v>
+      </c>
+      <c r="C534" t="s">
+        <v>5</v>
+      </c>
+      <c r="D534" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A535">
+        <v>64592</v>
+      </c>
+      <c r="B535" t="s">
+        <v>4</v>
+      </c>
+      <c r="C535" t="s">
+        <v>5</v>
+      </c>
+      <c r="D535" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A536">
+        <v>64593</v>
+      </c>
+      <c r="B536" t="s">
+        <v>4</v>
+      </c>
+      <c r="C536" t="s">
+        <v>5</v>
+      </c>
+      <c r="D536" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A537">
+        <v>64595</v>
+      </c>
+      <c r="B537" t="s">
+        <v>4</v>
+      </c>
+      <c r="C537" t="s">
+        <v>5</v>
+      </c>
+      <c r="D537" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A538">
+        <v>64604</v>
+      </c>
+      <c r="B538" t="s">
+        <v>13</v>
+      </c>
+      <c r="C538" t="s">
+        <v>14</v>
+      </c>
+      <c r="D538" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A539">
+        <v>64646</v>
+      </c>
+      <c r="B539" t="s">
+        <v>4</v>
+      </c>
+      <c r="C539" t="s">
+        <v>5</v>
+      </c>
+      <c r="D539" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A540">
+        <v>64694</v>
+      </c>
+      <c r="B540" t="s">
+        <v>4</v>
+      </c>
+      <c r="C540" t="s">
+        <v>5</v>
+      </c>
+      <c r="D540" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A541">
+        <v>65006</v>
+      </c>
+      <c r="B541" t="s">
+        <v>4</v>
+      </c>
+      <c r="C541" t="s">
+        <v>5</v>
+      </c>
+      <c r="D541" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A542">
+        <v>65007</v>
+      </c>
+      <c r="B542" t="s">
+        <v>4</v>
+      </c>
+      <c r="C542" t="s">
+        <v>5</v>
+      </c>
+      <c r="D542" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A543">
+        <v>65008</v>
+      </c>
+      <c r="B543" t="s">
+        <v>4</v>
+      </c>
+      <c r="C543" t="s">
+        <v>5</v>
+      </c>
+      <c r="D543" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A544">
+        <v>65214</v>
+      </c>
+      <c r="B544" t="s">
+        <v>4</v>
+      </c>
+      <c r="C544" t="s">
+        <v>5</v>
+      </c>
+      <c r="D544" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A545">
+        <v>65347</v>
+      </c>
+      <c r="B545" t="s">
+        <v>4</v>
+      </c>
+      <c r="C545" t="s">
+        <v>5</v>
+      </c>
+      <c r="D545" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A546">
+        <v>65375</v>
+      </c>
+      <c r="B546" t="s">
+        <v>4</v>
+      </c>
+      <c r="C546" t="s">
+        <v>5</v>
+      </c>
+      <c r="D546" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A547">
+        <v>65427</v>
+      </c>
+      <c r="B547" t="s">
+        <v>4</v>
+      </c>
+      <c r="C547" t="s">
+        <v>5</v>
+      </c>
+      <c r="D547" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A548">
+        <v>65506</v>
+      </c>
+      <c r="B548" t="s">
+        <v>4</v>
+      </c>
+      <c r="C548" t="s">
+        <v>5</v>
+      </c>
+      <c r="D548" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A549">
+        <v>65516</v>
+      </c>
+      <c r="B549" t="s">
+        <v>13</v>
+      </c>
+      <c r="C549" t="s">
+        <v>14</v>
+      </c>
+      <c r="D549" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A550">
+        <v>65517</v>
+      </c>
+      <c r="B550" t="s">
+        <v>13</v>
+      </c>
+      <c r="C550" t="s">
+        <v>14</v>
+      </c>
+      <c r="D550" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A551">
+        <v>65657</v>
+      </c>
+      <c r="B551" t="s">
+        <v>4</v>
+      </c>
+      <c r="C551" t="s">
+        <v>5</v>
+      </c>
+      <c r="D551" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A552">
+        <v>65658</v>
+      </c>
+      <c r="B552" t="s">
+        <v>4</v>
+      </c>
+      <c r="C552" t="s">
+        <v>5</v>
+      </c>
+      <c r="D552" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A553">
+        <v>65670</v>
+      </c>
+      <c r="B553" t="s">
+        <v>4</v>
+      </c>
+      <c r="C553" t="s">
+        <v>5</v>
+      </c>
+      <c r="D553" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A554">
+        <v>65797</v>
+      </c>
+      <c r="B554" t="s">
+        <v>4</v>
+      </c>
+      <c r="C554" t="s">
+        <v>5</v>
+      </c>
+      <c r="D554" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A555">
+        <v>65891</v>
+      </c>
+      <c r="B555" t="s">
+        <v>4</v>
+      </c>
+      <c r="C555" t="s">
+        <v>5</v>
+      </c>
+      <c r="D555" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A556">
+        <v>65909</v>
+      </c>
+      <c r="B556" t="s">
+        <v>4</v>
+      </c>
+      <c r="C556" t="s">
+        <v>5</v>
+      </c>
+      <c r="D556" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A557">
+        <v>65917</v>
+      </c>
+      <c r="B557" t="s">
+        <v>4</v>
+      </c>
+      <c r="C557" t="s">
+        <v>5</v>
+      </c>
+      <c r="D557" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A558">
+        <v>65918</v>
+      </c>
+      <c r="B558" t="s">
+        <v>4</v>
+      </c>
+      <c r="C558" t="s">
+        <v>5</v>
+      </c>
+      <c r="D558" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A559">
+        <v>66000</v>
+      </c>
+      <c r="B559" t="s">
+        <v>4</v>
+      </c>
+      <c r="C559" t="s">
+        <v>5</v>
+      </c>
+      <c r="D559" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A560">
+        <v>66072</v>
+      </c>
+      <c r="B560" t="s">
+        <v>13</v>
+      </c>
+      <c r="C560" t="s">
+        <v>14</v>
+      </c>
+      <c r="D560" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A561">
+        <v>66090</v>
+      </c>
+      <c r="B561" t="s">
+        <v>4</v>
+      </c>
+      <c r="C561" t="s">
+        <v>5</v>
+      </c>
+      <c r="D561" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A562">
+        <v>66116</v>
+      </c>
+      <c r="B562" t="s">
+        <v>13</v>
+      </c>
+      <c r="C562" t="s">
+        <v>14</v>
+      </c>
+      <c r="D562" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A563">
+        <v>66117</v>
+      </c>
+      <c r="B563" t="s">
+        <v>13</v>
+      </c>
+      <c r="C563" t="s">
+        <v>14</v>
+      </c>
+      <c r="D563" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A564">
+        <v>66146</v>
+      </c>
+      <c r="B564" t="s">
+        <v>4</v>
+      </c>
+      <c r="C564" t="s">
+        <v>5</v>
+      </c>
+      <c r="D564" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A565">
+        <v>66147</v>
+      </c>
+      <c r="B565" t="s">
+        <v>4</v>
+      </c>
+      <c r="C565" t="s">
+        <v>5</v>
+      </c>
+      <c r="D565" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A566">
+        <v>66402</v>
+      </c>
+      <c r="B566" t="s">
+        <v>4</v>
+      </c>
+      <c r="C566" t="s">
+        <v>5</v>
+      </c>
+      <c r="D566" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A567">
+        <v>66403</v>
+      </c>
+      <c r="B567" t="s">
+        <v>4</v>
+      </c>
+      <c r="C567" t="s">
+        <v>5</v>
+      </c>
+      <c r="D567" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A568">
+        <v>66404</v>
+      </c>
+      <c r="B568" t="s">
+        <v>4</v>
+      </c>
+      <c r="C568" t="s">
+        <v>5</v>
+      </c>
+      <c r="D568" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A569">
+        <v>66409</v>
+      </c>
+      <c r="B569" t="s">
+        <v>4</v>
+      </c>
+      <c r="C569" t="s">
+        <v>5</v>
+      </c>
+      <c r="D569" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A570">
+        <v>66564</v>
+      </c>
+      <c r="B570" t="s">
+        <v>4</v>
+      </c>
+      <c r="C570" t="s">
+        <v>5</v>
+      </c>
+      <c r="D570" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A571">
+        <v>66565</v>
+      </c>
+      <c r="B571" t="s">
+        <v>4</v>
+      </c>
+      <c r="C571" t="s">
+        <v>5</v>
+      </c>
+      <c r="D571" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A572">
+        <v>66587</v>
+      </c>
+      <c r="B572" t="s">
+        <v>4</v>
+      </c>
+      <c r="C572" t="s">
+        <v>5</v>
+      </c>
+      <c r="D572" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A573">
+        <v>66680</v>
+      </c>
+      <c r="B573" t="s">
+        <v>4</v>
+      </c>
+      <c r="C573" t="s">
+        <v>5</v>
+      </c>
+      <c r="D573" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A574">
+        <v>66810</v>
+      </c>
+      <c r="B574" t="s">
+        <v>4</v>
+      </c>
+      <c r="C574" t="s">
+        <v>5</v>
+      </c>
+      <c r="D574" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A575">
+        <v>66884</v>
+      </c>
+      <c r="B575" t="s">
+        <v>4</v>
+      </c>
+      <c r="C575" t="s">
+        <v>5</v>
+      </c>
+      <c r="D575" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A576">
+        <v>66912</v>
+      </c>
+      <c r="B576" t="s">
+        <v>4</v>
+      </c>
+      <c r="C576" t="s">
+        <v>5</v>
+      </c>
+      <c r="D576" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A577">
+        <v>66930</v>
+      </c>
+      <c r="B577" t="s">
+        <v>4</v>
+      </c>
+      <c r="C577" t="s">
+        <v>5</v>
+      </c>
+      <c r="D577" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A578">
+        <v>67331</v>
+      </c>
+      <c r="B578" t="s">
+        <v>4</v>
+      </c>
+      <c r="C578" t="s">
+        <v>5</v>
+      </c>
+      <c r="D578" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A579">
+        <v>67353</v>
+      </c>
+      <c r="B579" t="s">
+        <v>4</v>
+      </c>
+      <c r="C579" t="s">
+        <v>5</v>
+      </c>
+      <c r="D579" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A580">
+        <v>67354</v>
+      </c>
+      <c r="B580" t="s">
+        <v>4</v>
+      </c>
+      <c r="C580" t="s">
+        <v>5</v>
+      </c>
+      <c r="D580" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A581">
+        <v>67366</v>
+      </c>
+      <c r="B581" t="s">
+        <v>13</v>
+      </c>
+      <c r="C581" t="s">
+        <v>14</v>
+      </c>
+      <c r="D581" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A582">
+        <v>67388</v>
+      </c>
+      <c r="B582" t="s">
+        <v>4</v>
+      </c>
+      <c r="C582" t="s">
+        <v>5</v>
+      </c>
+      <c r="D582" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A583">
+        <v>67402</v>
+      </c>
+      <c r="B583" t="s">
+        <v>4</v>
+      </c>
+      <c r="C583" t="s">
+        <v>5</v>
+      </c>
+      <c r="D583" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A584">
+        <v>67510</v>
+      </c>
+      <c r="B584" t="s">
+        <v>4</v>
+      </c>
+      <c r="C584" t="s">
+        <v>5</v>
+      </c>
+      <c r="D584" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A585">
+        <v>67511</v>
+      </c>
+      <c r="B585" t="s">
+        <v>4</v>
+      </c>
+      <c r="C585" t="s">
+        <v>5</v>
+      </c>
+      <c r="D585" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A586">
+        <v>67532</v>
+      </c>
+      <c r="B586" t="s">
+        <v>4</v>
+      </c>
+      <c r="C586" t="s">
+        <v>5</v>
+      </c>
+      <c r="D586" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A587">
+        <v>67676</v>
+      </c>
+      <c r="B587" t="s">
+        <v>4</v>
+      </c>
+      <c r="C587" t="s">
+        <v>5</v>
+      </c>
+      <c r="D587" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A588">
+        <v>67865</v>
+      </c>
+      <c r="B588" t="s">
+        <v>4</v>
+      </c>
+      <c r="C588" t="s">
+        <v>5</v>
+      </c>
+      <c r="D588" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A589">
+        <v>67935</v>
+      </c>
+      <c r="B589" t="s">
+        <v>4</v>
+      </c>
+      <c r="C589" t="s">
+        <v>5</v>
+      </c>
+      <c r="D589" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A590">
+        <v>67944</v>
+      </c>
+      <c r="B590" t="s">
+        <v>4</v>
+      </c>
+      <c r="C590" t="s">
+        <v>5</v>
+      </c>
+      <c r="D590" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A591">
+        <v>67945</v>
+      </c>
+      <c r="B591" t="s">
+        <v>4</v>
+      </c>
+      <c r="C591" t="s">
+        <v>5</v>
+      </c>
+      <c r="D591" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A592">
+        <v>67946</v>
+      </c>
+      <c r="B592" t="s">
+        <v>4</v>
+      </c>
+      <c r="C592" t="s">
+        <v>5</v>
+      </c>
+      <c r="D592" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A593">
+        <v>67947</v>
+      </c>
+      <c r="B593" t="s">
+        <v>13</v>
+      </c>
+      <c r="C593" t="s">
+        <v>14</v>
+      </c>
+      <c r="D593" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A594">
+        <v>67970</v>
+      </c>
+      <c r="B594" t="s">
+        <v>4</v>
+      </c>
+      <c r="C594" t="s">
+        <v>5</v>
+      </c>
+      <c r="D594" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A595">
+        <v>67980</v>
+      </c>
+      <c r="B595" t="s">
+        <v>4</v>
+      </c>
+      <c r="C595" t="s">
+        <v>5</v>
+      </c>
+      <c r="D595" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A596">
+        <v>67985</v>
+      </c>
+      <c r="B596" t="s">
+        <v>4</v>
+      </c>
+      <c r="C596" t="s">
+        <v>5</v>
+      </c>
+      <c r="D596" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A597">
+        <v>67990</v>
+      </c>
+      <c r="B597" t="s">
+        <v>4</v>
+      </c>
+      <c r="C597" t="s">
+        <v>5</v>
+      </c>
+      <c r="D597" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A598">
+        <v>67991</v>
+      </c>
+      <c r="B598" t="s">
+        <v>4</v>
+      </c>
+      <c r="C598" t="s">
+        <v>5</v>
+      </c>
+      <c r="D598" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A599">
+        <v>68031</v>
+      </c>
+      <c r="B599" t="s">
+        <v>4</v>
+      </c>
+      <c r="C599" t="s">
+        <v>5</v>
+      </c>
+      <c r="D599" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A600">
+        <v>68032</v>
+      </c>
+      <c r="B600" t="s">
+        <v>4</v>
+      </c>
+      <c r="C600" t="s">
+        <v>5</v>
+      </c>
+      <c r="D600" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A601">
+        <v>68114</v>
+      </c>
+      <c r="B601" t="s">
+        <v>4</v>
+      </c>
+      <c r="C601" t="s">
+        <v>5</v>
+      </c>
+      <c r="D601" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A602">
+        <v>68160</v>
+      </c>
+      <c r="B602" t="s">
+        <v>4</v>
+      </c>
+      <c r="C602" t="s">
+        <v>5</v>
+      </c>
+      <c r="D602" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A603">
+        <v>68171</v>
+      </c>
+      <c r="B603" t="s">
+        <v>4</v>
+      </c>
+      <c r="C603" t="s">
+        <v>5</v>
+      </c>
+      <c r="D603" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A604">
+        <v>68172</v>
+      </c>
+      <c r="B604" t="s">
+        <v>4</v>
+      </c>
+      <c r="C604" t="s">
+        <v>5</v>
+      </c>
+      <c r="D604" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A605">
+        <v>68173</v>
+      </c>
+      <c r="B605" t="s">
+        <v>4</v>
+      </c>
+      <c r="C605" t="s">
+        <v>5</v>
+      </c>
+      <c r="D605" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A606">
+        <v>68214</v>
+      </c>
+      <c r="B606" t="s">
+        <v>4</v>
+      </c>
+      <c r="C606" t="s">
+        <v>5</v>
+      </c>
+      <c r="D606" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A607">
+        <v>68215</v>
+      </c>
+      <c r="B607" t="s">
+        <v>4</v>
+      </c>
+      <c r="C607" t="s">
+        <v>5</v>
+      </c>
+      <c r="D607" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A608">
+        <v>68216</v>
+      </c>
+      <c r="B608" t="s">
+        <v>4</v>
+      </c>
+      <c r="C608" t="s">
+        <v>5</v>
+      </c>
+      <c r="D608" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A609">
+        <v>68328</v>
+      </c>
+      <c r="B609" t="s">
+        <v>4</v>
+      </c>
+      <c r="C609" t="s">
+        <v>5</v>
+      </c>
+      <c r="D609" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A610">
+        <v>68329</v>
+      </c>
+      <c r="B610" t="s">
+        <v>4</v>
+      </c>
+      <c r="C610" t="s">
+        <v>5</v>
+      </c>
+      <c r="D610" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A611">
+        <v>68330</v>
+      </c>
+      <c r="B611" t="s">
+        <v>4</v>
+      </c>
+      <c r="C611" t="s">
+        <v>5</v>
+      </c>
+      <c r="D611" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A612">
+        <v>68331</v>
+      </c>
+      <c r="B612" t="s">
+        <v>4</v>
+      </c>
+      <c r="C612" t="s">
+        <v>5</v>
+      </c>
+      <c r="D612" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A613">
+        <v>68366</v>
+      </c>
+      <c r="B613" t="s">
+        <v>4</v>
+      </c>
+      <c r="C613" t="s">
+        <v>5</v>
+      </c>
+      <c r="D613" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A614">
+        <v>68374</v>
+      </c>
+      <c r="B614" t="s">
+        <v>4</v>
+      </c>
+      <c r="C614" t="s">
+        <v>5</v>
+      </c>
+      <c r="D614" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A615">
+        <v>68482</v>
+      </c>
+      <c r="B615" t="s">
+        <v>4</v>
+      </c>
+      <c r="C615" t="s">
+        <v>5</v>
+      </c>
+      <c r="D615" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A616">
+        <v>68510</v>
+      </c>
+      <c r="B616" t="s">
+        <v>4</v>
+      </c>
+      <c r="C616" t="s">
+        <v>5</v>
+      </c>
+      <c r="D616" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A617">
+        <v>68517</v>
+      </c>
+      <c r="B617" t="s">
+        <v>4</v>
+      </c>
+      <c r="C617" t="s">
+        <v>5</v>
+      </c>
+      <c r="D617" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A618">
+        <v>68531</v>
+      </c>
+      <c r="B618" t="s">
+        <v>4</v>
+      </c>
+      <c r="C618" t="s">
+        <v>5</v>
+      </c>
+      <c r="D618" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A619">
+        <v>68711</v>
+      </c>
+      <c r="B619" t="s">
+        <v>4</v>
+      </c>
+      <c r="C619" t="s">
+        <v>5</v>
+      </c>
+      <c r="D619" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A620">
+        <v>68746</v>
+      </c>
+      <c r="B620" t="s">
+        <v>4</v>
+      </c>
+      <c r="C620" t="s">
+        <v>5</v>
+      </c>
+      <c r="D620" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A621">
+        <v>68751</v>
+      </c>
+      <c r="B621" t="s">
+        <v>4</v>
+      </c>
+      <c r="C621" t="s">
+        <v>5</v>
+      </c>
+      <c r="D621" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A622">
+        <v>68819</v>
+      </c>
+      <c r="B622" t="s">
+        <v>4</v>
+      </c>
+      <c r="C622" t="s">
+        <v>5</v>
+      </c>
+      <c r="D622" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A623">
+        <v>68862</v>
+      </c>
+      <c r="B623" t="s">
+        <v>4</v>
+      </c>
+      <c r="C623" t="s">
+        <v>5</v>
+      </c>
+      <c r="D623" t="s">
+        <v>629</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
